--- a/excel/스포짐_기획문서_v2.xlsx
+++ b/excel/스포짐_기획문서_v2.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2443,6 +2443,1836 @@
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GX 예약</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GX 예약 관리</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>/schedule/gx-booking</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>매니저 이상</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>GX 프로그램 예약 오픈/관리. N시간 전 자동 오픈, 노쇼 페널티, 출석체크 연동</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>레슨북/온핏 장점 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>좌석 예약</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>좌석 예약 관리</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>/schedule/seat-booking</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>매니저 이상</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>스피닝/GX 좌석 지정 예약. 바이크 번호별 예약/고장 관리</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>판교점/용산점 요구사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>레슨 관리</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SCR-024</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>레슨 기록/서명</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>/schedule/lesson</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>트레이너 이상</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PT/골프 레슨 기록, 고객 서명 확인, 수업 진위 관리</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>레슨북 장점 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>타석</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SCR-054</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>골프 타석 관리</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>/facility/golf-bay</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>매니저 이상</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>골프 타석 예약/대기/제어. 꼬리물기 예약, 시간관리</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>대치점 브로제이 장점 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전원제어</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SCR-055</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>기기 전원 제어</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>/facility/power-control</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>매니저 이상</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>키오스크/프로젝터 원격 전원 ON/OFF, 스케줄 자동 제어</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>고척점/대치점 핵심 요구사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>수건/운동복</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SCR-056</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>수건/운동복 관리</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>/facility/towel</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>스태프 이상</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>수건/운동복 발급 관리. QR/안면인식 연동, 수량 제한, 사용량 통계</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>양천향교점 벤치마크</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FC 알림</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기/알림</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>/members/fc-alert</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FC 이상</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>담당 FC별 즐겨찾기 회원 등록, 방문 시 실시간 알림, 임박회원 자동 알림</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>대치점 온핏 핵심 기능</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>키오스크 타입</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SCR-095</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>키오스크 타입 설정</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>/settings/kiosk-type</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>센터장 이상</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>키오스크 타입(결제형/비결제형) 지점별 설정. UI 화면 구성 분기</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>판교점 인터뷰 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>오프라인</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SCR-096</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>오프라인 모드 설정</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>/settings/offline</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>센터장 이상</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>네트워크 장애 시 로컬 모드 동작 설정. 자동 동기화 정책</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>전 지점 공통 요구사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>매출/결제</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>통합 내보내기</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SCR-033</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>데이터 통합 내보내기</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>/sales/export</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>매니저 이상</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>모든 데이터 원장 엑셀 내보내기. 권한별 컬럼 필터, 전체 필드 포함</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>고척점 레슨북 장점 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>입장</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SCR-K01</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>키오스크 입장</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>/kiosk/entry</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>회원 입장 화면. 얼굴인식/전화번호/NFC 밴드 입장. 지점별 타입(A/B) 분기</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>대치점 브로제이 벤치마크</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>퇴장</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SCR-K02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>키오스크 퇴장</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>/kiosk/exit</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>회원 퇴장 처리. 라커 자동 해제, 이용시간 기록</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>판교점 온핏</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>골프 예약</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SCR-K03</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 예약</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>/kiosk/golf-booking</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>골프 타석 예약/대기. 빈 타석 표시, 꼬리물기 예약, 잔여시간(시:분 표시)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>대치점 브로제이</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>사물함</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SCR-K04</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>키오스크 사물함 확인</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>/kiosk/locker</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>배정된 라커 번호 확인. 영수증 출력(대치점 방식)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>대치점</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1일권 결제</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SCR-K05</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>키오스크 1일권 결제</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>/kiosk/day-pass</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1일권/시간권 현장 결제(타입B 전용). 가상 회원ID 자동 생성, 카드/간편결제</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>판교점 인터뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GX 예약</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SCR-K06</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>키오스크 GX 예약</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>/kiosk/gx-booking</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>GX 프로그램 예약/취소. 잔여 좌석 표시, 좌석 선택(스피닝)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>판교점 온핏</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>골프 입장</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SCR-K07</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 입장</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>/kiosk/golf-entry</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>예약한 골프 타석 입장. 전화번호 인증 → 스크린 잠금 해제 → 이용 시작</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>대치점 브로제이</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>홈</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SCR-M01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>앱 홈</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>/app/home</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>회원 앱 메인. 이용권 잔여일, 출석 현황, 예약 내역, 공지사항</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>입장/퇴장</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SCR-M02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>앱 QR 입장</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>/app/checkin</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>QR코드/NFC 기반 센터 입장. 라커 번호 표시, 입장 시간 기록</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GX 예약</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SCR-M03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>앱 GX 예약</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>/app/gx-booking</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>GX 프로그램 예약/취소. 주간 시간표, 잔여석, 좌석 선택(스피닝 배치도)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>판교점 온핏 앱</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>골프 예약</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SCR-M04</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>앱 골프 타석 예약</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>/app/golf-booking</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>골프 타석 원격 예약/대기. 실시간 타석 현황, 잔여시간(시:분), 푸시 알림</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>레슨 예약</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SCR-M05</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>앱 레슨 예약/서명</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>/app/lesson</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PT/골프 레슨 예약, 수업 후 서명 확인, 레슨 기록 열람, 잔여 횟수 확인</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>내 정보</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SCR-M06</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>앱 내 정보</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>/app/profile</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>이용권 현황, 결제 내역, 출석 이력, 체성분 변화 추이, 포인트/쿠폰</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SCR-M07</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>앱 알림 센터</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>/app/notifications</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>예약 리마인드, 이용권 만료 안내, 프로모션, GX 오픈 알림</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>홈</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SCR-T01</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>트레이너 앱 홈</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>/trainer/home</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>오늘의 수업 목록, 예약 현황, 미완료 레슨 기록 알림</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>스케줄</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SCR-T02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>트레이너 스케줄</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>/trainer/schedule</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>주간/월간 수업 캘린더. 수업 상세, 회원 정보, 예약/취소/노쇼 표시</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>레슨 기록</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SCR-T03</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>트레이너 레슨 기록</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>/trainer/lesson-record</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>수업 내용 작성(텍스트/템플릿), 고객 터치 서명, 사진 첨부, 수업 완료 처리</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>회원 관리</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SCR-T04</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>트레이너 담당 회원</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>/trainer/members</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>담당 회원 목록, 잔여 횟수, 레슨 이력, 다음 예약, 메모</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>고척점 레슨북</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>홈</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SCR-F01</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FC 앱 홈</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>/fc/home</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>오늘 방문 알림, 임박 회원 목록, 개인 매출 현황, 상담 일정</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>대치점 온핏</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>즐겨찾기</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SCR-F02</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기 알림</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>/fc/favorites</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>즐겨찾기 회원 관리, 방문 실시간 푸시 알림, 잔여일/미납 표시, 상담 메모</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>대치점 온핏 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>회원 상담</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SCR-F03</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FC 회원 상담 기록</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>/fc/consultation</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>상담 내용 기록, 재등록 상담 이력, 실적 귀속 확인, 프로모션 안내</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>서교점 인터뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SCR-F04</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FC 개인 매출</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>/fc/sales</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>개인 매출/팀 매출 현황, 실적 담당 건 목록, 월별 추이, 목표 달성률</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>서교점 인터뷰</t>
         </is>
       </c>
     </row>
@@ -2469,7 +4299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4288,6 +6118,930 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BP-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>오프라인 모드 정책</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>네트워크 장애 시 로컬 모드 자동 전환. 필수 기능(출입/라커/출석)은 오프라인에서도 동작. 로컬 데이터 최대 72시간 보관. 네트워크 복구 시 자동 동기화(서버 우선). 오프라인 불가 기능: 결제/환불/회원등록. 동기화 충돌 시 관리자 알림.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SCR-096</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FN-047</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BP-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GX 예약 오픈 정책</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GX 수업 예약 오픈 방식 2가지 지원: 1) 일괄 오픈(매주 특정 요일/시간에 다음주 전체 오픈), 2) 개별 오픈(수업 시작 N시간 전 자동 오픈). 센터별 방식 선택. 예약 오픈 시 회원 앱 알림 발송(설정 시). 강사 변경 시 일괄 수정 지원(기간 지정).</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FN-034</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BP-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GX/스피닝 노쇼 페널티 정책</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>취소 가능 시한: 수업 시작 N시간 전(기본 5시간, 센터 설정). 시한 내 취소: 횟수 미차감. 시한 초과 취소 또는 노쇼: 1회 차감(수업 진행 처리). 월 N회(기본 2회) 노쇼 시 1주간 예약 제한 페널티. 페널티 부과 전 회원 알림 발송. 출석 체크 없이 하루 경과 시 자동 수업 완료 처리(레슨북 방식).</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FN-036</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BP-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>좌석 예약 정책</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>스피닝/GX 좌석 예약 선착순 방식. 예약 시간순으로 좌석 선택 우선권 부여. 고장 좌석: 관리자만 비활성화(사선 표시), 기예약자 자동 알림. 좌석 미선택 시 자동 랜덤 배정. 센터별 좌석 예약 ON/OFF 설정 가능.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FN-037</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BP-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>레슨 서명 정책</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PT/골프 레슨 완료 시 고객 터치 서명으로 수업 진위 확인. 서명 필수 여부: 센터별 ON/OFF 설정. 서명 필수 ON: 서명 없으면 수업 인정 불가, 관리자 확인 필요. 서명 없이 24시간 경과: 자동 수업 완료(센터 설정에 따라). 노쇼 = 수업 진행 처리(횟수 차감). 취소 = 횟수 미차감(시한 내).</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SCR-024</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FN-039</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BP-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>라커 배정 우선순위 정책</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>자동 배정 시 우선순위: 상단 &gt; 하단, 홀수 &gt; 짝수(센터 설정). 고장/점유 라커 자동 스킵. 퇴실 시 라커 자동 해제 여부 센터 설정. 마감 시 전체 라커 일괄 해제 기능 제공. 잔류물: 프론트 보관 15일 → 폐기. NFC/번호키/일반키 방식 센터별 선택 가능(표준: NFC 랜덤배정 또는 번호키 고정배정 2가지).</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SCR-050</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FN-050</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BP-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>키오스크 타입 정책</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2가지 타입: 타입A(입퇴장/사물함 전용, 결제 없음), 타입B(1일권/시간권 현장 결제 포함). 지점 단위 설정(어드민). 타입B: PG사 결제 모듈 연동 필수. 타입별 키오스크 UI 자동 분기. 1일권 결제 시 가상 회원ID 자동 생성 + 당일 만료.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SCR-095</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FN-046</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BP-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>기기 전원 제어 정책</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>키오스크: WOL(Wake-on-LAN) 원격 부팅/셧다운. 프로젝터: PJ Link 프로토콜 제어. 스케줄 설정: 오픈 N분 전 자동 부팅, 마감 시 자동 셧다운. 기기 상태 실시간 모니터링(온라인/오프라인/고장). 미응답 기기 3회 재시도 후 오프라인 표시 + 관리자 알림. 골프장 전 지점 적용 권장(연간 인건비 절감 효과).</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SCR-055</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FN-043</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BP-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>수건/운동복 발급 정책</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>기본 제공량: 수건 2장 + 운동복 1벌/일(센터 설정). 추가 발급: 유/무료 센터 설정. 발급 방식: QR 스캔/안면인식/NFC 택 1(센터 설정). 반납 시 포인트 적립 옵션. 과다 발급 알림: 평균 대비 150% 초과 시 관리자 알림. 월간 세탁비 자동 집계 + 입장객 대비 사용률 통계.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SCR-056</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FN-044</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BP-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기 알림 정책</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FC 개인 아이디별 즐겨찾기 회원 등록(수 제한 없음). 즐겨찾기 회원 입장 시 해당 FC에 실시간 푸시 알림(앱 푸시 + 관리자 화면 팝업). 알림 내용: 회원명, 잔여 이용권일수, 미납 여부. 이용권 만료 D-30 이내 회원 자동 즐겨찾기 추가(설정 시). 담당 FC 퇴사 시 즐겨찾기 재배정.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FN-045</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BP-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>실적 귀속 정책</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>최초 상담자에게 실적 귀속(기본). 귀속 유효기간: 상담일로부터 N일(기본 30일, 센터 설정). 유효기간 초과 시 귀속 해제, 새 상담자에게 이전. 계약 처리자 ≠ 실적 담당자 분리 가능. 실적: 개인 매출 + 팀 매출 이중 집계. 분쟁 방지: 상담 이력(일시/내용) 자동 기록.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SCR-030</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FN-051</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BP-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>프로모션 할인 자동화 정책</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>프로모션 사전 등록: 기간/대상(신규/재등록/휴면복귀)/할인율 설정. 계약 시 해당 프로모션 자동 적용(수동 입력 불필요). FC 재량 할인: 센터장이 최대 한도 설정(예: 5%). 할인율 50% 초과: 센터장 승인 필요. 프로모션 중복 적용 불가(최대 혜택 자동 선택). 할인 적용 시 원가/할인가/최종가 모두 표시. 전체 할인 이력 감사 로그.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SCR-041</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FN-052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BP-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>출석/일정</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GX 출석 체크 정책</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>출석 체크 방식: QR코드(권장, 저비용) / NFC / 안면인식 / 수동. 전 매장 표준: QR코드 리더기 설치 권장. 센터 입장(키오스크) + 프로그램 예약 매칭 → 자동 출석 처리. 예약 후 미출석(수업 종료 시점): 노쇼 자동 처리. 비예약자 참석 감지 시 FC 알림(영업 기회).</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FN-035</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BP-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>키오스크 입장 인증 정책</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>인증 방식 3가지 지원: 얼굴인식(브로제이 방식)/전화번호/NFC밴드(온핏 방식). 센터별 기본 인증 방식 설정. 얼굴인식 실패 시 전화번호 폴백. 동시 다중 인식 지원(얼굴인식). 만료 회원 입장: 센터 설정(허용/경고후허용/차단). 입장 시 라커 자동 배정(배정 규칙에 따라).</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SCR-K01</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FN-K01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BP-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>키오스크 퇴장/라커 해제 정책</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>퇴장 방식: 인증 퇴장 or 라커키 반납 퇴장(대치점 방식). 퇴장 시 라커 자동 해제(센터 설정). 퇴장 미처리 시 마감 일괄 퇴장 처리. 이용시간 자동 기록(입장~퇴장). 라커 잔류물: 마감 시 체크리스트 생성.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SCR-K02</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FN-K02</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BP-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>골프 타석 시간 표시 정책</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>대기시간/잔여시간 표시: 시:분 형식(예: 3시간 58분). 분 단위 표시 금지(238분 X). 60분 이하: 분만 표시(예: 45분). 1회 이용시간: 최대 60분(센터 설정 가능). 이용 종료 10분 전 화면 알림. 시간 종료 시 자동 스크린 잠금.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SCR-K03, SCR-K07</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FN-K03, FN-K07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BP-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>사물함 영수증 정책</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>대치점 벤치마크: 라커 배정 시 영수증 형태로 라커 번호 출력. 영수증에 라커 번호 크게 표시(고령 회원 배려). 라커 위치 안내(층/구역) 포함. 영수증 미수령 시 키오스크에서 재확인 가능. 분실 시 전화번호로 재조회.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SCR-K04</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FN-K04</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BP-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>회원 앱 QR 입장 정책</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>QR코드: 일회용, 30초마다 자동 갱신(보안). QR 생성: 로그인 상태에서만 가능. 오프라인 시 QR 생성 불가(네트워크 필수). QR 스캔 → 입장 처리 + 라커 배정 동시 처리. QR 입장은 키오스크 얼굴인식/NFC와 동일 권한.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SCR-M02</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FN-M02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BP-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>앱 원격 예약 정책</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GX/골프/PT 앱 원격 예약 가능. GX: 예약 오픈 시 앱 푸시 알림 → 선착순 예약. 골프: 원격 대기열 등록 → 순번 도달 시 푸시 알림 → 15분 이내 입장 필수. PT: 트레이너 빈 시간대에서 예약 → 트레이너 승인 필요(센터 설정). 취소 시한/노쇼 페널티는 관리자 정책과 동일 적용.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SCR-M03, SCR-M04, SCR-M05</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FN-M03, FN-M04, FN-M05</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BP-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>트레이너 레슨 기록 정책</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>수업 완료 후 당일 내 레슨 기록 작성 권장. 3일 초과 미작성 시 관리자 알림. 고객 서명: 수업 완료 시 요청 → 고객 앱 or 현장 태블릿에서 서명. 서명 필수 여부: 센터별 ON/OFF. 미서명 24시간 경과: 정책에 따라 자동 완료 or 관리자 확인. 레슨 기록 수정: 작성 후 24시간 이내만 가능.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SCR-T03</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FN-T02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BP-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FC 방문 알림 정책</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>즐겨찾기 회원 입장 시 해당 FC에 30초 이내 푸시 알림. 알림 내용: 회원명, 잔여 이용권일수, 미납 여부, 마지막 방문일. 알림 채널: 앱 푸시(필수) + 관리자 Web 팝업(선택). 알림 수신 거부 시 앱 내 배지만 표시. 비근무 시간 알림: 앱 내 축적, 출근 시 일괄 확인.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SCR-F01, SCR-F02</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FN-F01, FN-F02</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BP-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>상담 이력 및 실적 귀속 정책(앱)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>모든 상담은 일시/내용/결과 기록 필수. 최초 상담자 자동 기록 → 실적 귀속 근거. 상담 기록 수정: 24시간 이내만 가능(감사 로그). 동일 회원 타 FC 상담 이력 참조 가능(내용은 비공개 옵션). 상담 → 계약 전환율 자동 집계. 실적 귀속 잔여일수 앱에 표시(예: 'D-15 귀속 만료').</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SCR-F03</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FN-F03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4300,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6245,6 +8999,1307 @@
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>US-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>매니저로서 GX 수업 예약을 N시간 전 자동 오픈 설정하여 수작업을 줄이고 싶다</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1) 수업별 예약 오픈 시간(N시간 전) 설정 가능
+2) 일괄 오픈(매주 특정 요일/시간) 설정 가능
+3) 강사 변경 시 기간 지정 일괄 변경 가능
+4) 예약 오픈 시 회원 앱 알림 발송</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>US-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>매니저로서 GX 출석을 QR/NFC로 자동 체크하여 노쇼를 정확히 파악하고 싶다</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1) QR/NFC 스캔으로 출석 자동 기록
+2) 센터 입장 + 프로그램 예약 매칭 자동 출석
+3) 노쇼 자동 감지 및 페널티 처리
+4) 비예약자 참석 시 FC 알림</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>US-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>회원으로서 스피닝 수업 예약 시 원하는 바이크 좌석을 선택하고 싶다</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1) 바이크 배치도에서 원하는 좌석 선택 가능
+2) 고장 좌석 비활성화 표시(선택 불가)
+3) 예약 순서에 따른 좌석 선택 우선권</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>US-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>트레이너로서 레슨 완료 후 고객 서명을 받아 수업 진위를 증명하고 싶다</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1) 수업 내용 기록 + 고객 터치 서명
+2) 서명 완료 시 수업 확정
+3) 모바일에서도 서명 가능
+4) 서명 이력 조회 가능</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SCR-024</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>US-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>센터장</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>센터장으로서 30개 이상의 키오스크/프로젝터를 원격으로 일괄 ON/OFF하여 오픈/마감 시간을 절약하고 싶다</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1) 관리 PC에서 전체/개별 전원 ON/OFF
+2) 오픈/마감 스케줄 자동 제어 설정
+3) 기기 상태 실시간 모니터링
+4) 미응답 기기 알림</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SCR-055</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>US-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>매니저로서 수건/운동복 발급을 자동화하여 과다 사용을 줄이고 세탁비를 관리하고 싶다</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1) 회원별 1일 발급 수량 제한
+2) QR/안면인식 발급 기록 자동화
+3) 월간 사용량 통계 + 세탁비 추정
+4) 과다 발급 알림</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SCR-056</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>US-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FC로서 담당 회원이 센터에 방문하면 즉시 알림을 받아 재등록 상담 타이밍을 놓치지 않고 싶다</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1) 즐겨찾기 회원 입장 시 핸드폰 푸시 알림
+2) 알림에 잔여일수/미납 여부 표시
+3) 이용권 만료 임박 회원 자동 즐겨찾기
+4) 방문 이력 기반 상담 포인트 제공</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>US-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>상품관리</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>매니저로서 상품을 한 화면에서 요일별/시간별/횟수별/기간별 세팅을 완료하고 싶다</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1) 팝업 없이 한 화면에서 전체 속성 설정
+2) 주중권/주말권 분기 설정
+3) 횟수제/기간제/혼합 선택
+4) 상품 클릭 시 구매 회원 바로 확인</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SCR-041</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>US-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>센터장</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>센터장으로서 키오스크 타입(결제형/비결제형)을 지점별로 설정하고 싶다</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1) 타입A(입퇴장 전용)/타입B(결제 포함) 선택
+2) 선택에 따라 키오스크 UI 자동 분기
+3) 타입B 시 1일권 현장 결제 가능</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SCR-095</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>US-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>센터장</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>센터장으로서 네트워크 장애 시에도 출입/라커 기본 기능이 동작하여 영업 중단을 방지하고 싶다</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1) 네트워크 끊김 시 자동 로컬 모드 전환
+2) 출입/라커/출석 오프라인 동작
+3) 네트워크 복구 시 자동 동기화
+4) 오프라인 상태 표시 배너</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SCR-096</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>US-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>매니저로서 라커 자동 배정 시 상단/홀수 우선 배정 규칙을 적용하여 회원 불만을 줄이고 싶다</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1) 상단&gt;하단, 홀수&gt;짝수 우선 배정
+2) 고장/점유 라커 자동 스킵
+3) 마감 시 전체 라커 일괄 해제
+4) 잔류물 체크리스트 제공</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SCR-050</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>US-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>매출관리</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FC로서 최초 상담한 회원의 실적이 정확히 나에게 귀속되길 원한다</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1) 최초 상담자 자동 실적 귀속
+2) 귀속 유효기간(N일) 설정
+3) 계약 처리자와 실적 담당자 분리 가능
+4) 상담 이력 자동 기록</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SCR-030</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>US-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>매출관리</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>매니저로서 전체 데이터를 엑셀 원장으로 내보내어 자유롭게 가공하고 싶다</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1) 회원/매출/출석/레슨 등 전체 원장 내보내기
+2) 모든 필드 포함(raw 데이터)
+3) 권한별 열람 가능 컬럼 자동 필터
+4) CSV/XLSX 포맷 선택</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SCR-033</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>US-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>매니저</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>매니저로서 골프 타석 예약 현황과 대기열을 실시간으로 관리하고 싶다</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1) 타석별 이용자/잔여시간 실시간 표시(시:분 형식)
+2) 꼬리물기 방식 예약
+3) 모바일 원격 예약 지원
+4) 15분 이내 미입장 시 노쇼 처리</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SCR-054</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>US-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>상품관리</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>센터장</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>센터장으로서 프로모션 할인율을 사전 설정하여 FC 수동 입력 오류를 방지하고 싶다</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1) 프로모션 기간/대상/할인율 사전 설정
+2) 계약 시 자동 적용
+3) FC 재량 할인 한도 설정
+4) 할인 50% 초과 시 승인 필요</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SCR-041</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>US-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>회원으로서 얼굴인식으로 빠르게 입장하고 라커 번호를 자동으로 배정받고 싶다</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1) 얼굴인식 → 즉시 입장
+2) 라커 자동 배정 + 번호 표시
+3) 영수증으로 라커 번호 출력(선택)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SCR-K01, SCR-K04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>US-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>비회원</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>비회원으로서 키오스크에서 1일권을 결제하고 바로 입장하고 싶다</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1) 전화번호 입력 → 상품 선택 → 카드 결제
+2) 결제 완료 → 라커 배정 → 입장
+3) 당일 자동 만료</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SCR-K05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>US-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>회원으로서 키오스크에서 골프 타석 대기시간을 시:분 형식으로 확인하고 싶다</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1) 타석별 잔여시간 '시간:분' 형식 표시
+2) 꼬리물기 예약 가능
+3) 15분 미입장 시 노쇼 안내</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SCR-K03, SCR-K07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>US-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>회원으로서 앱에서 QR코드로 센터에 입장하고 라커 번호를 확인하고 싶다</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1) 앱에서 QR 표시 → 리더기 스캔 → 입장
+2) 입장 후 배정된 라커 번호 앱에 표시
+3) QR 30초마다 자동 갱신</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SCR-M02</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>US-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>회원으로서 앱에서 GX 예약 오픈 알림을 받고 바로 스피닝 좌석을 선택하고 싶다</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1) GX 오픈 시 푸시 알림
+2) 앱에서 바이크 배치도 보고 좌석 선택
+3) 정원 초과 시 대기 등록 + 빈자리 알림</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SCR-M03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>US-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>회원으로서 앱에서 골프 타석 대기열에 원격 등록하고 순번 알림을 받고 싶다</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1) 앱에서 타석 현황 확인 → 대기 등록
+2) 순번 도달 시 푸시 알림
+3) 15분 이내 입장 필수</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SCR-M04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>US-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>회원으로서 PT 수업 후 앱에서 서명하여 레슨 기록을 확인하고 싶다</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1) 트레이너 서명 요청 → 앱 팝업
+2) 터치 서명으로 수업 확인
+3) 레슨 기록/잔여 횟수 열람</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SCR-M05</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>US-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>트레이너로서 앱에서 오늘 수업 목록을 확인하고 레슨 기록을 바로 작성하고 싶다</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1) 오늘 수업 타임라인 표시
+2) 수업 탭 → 레슨 기록 바로 작성
+3) 고객 서명 요청 원터치
+4) 미완료 기록 배지 알림</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SCR-T01, SCR-T03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>US-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>트레이너</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>트레이너로서 앱에서 빈 시간대를 관리하고 예약 요청을 승인/거절하고 싶다</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1) 주간/월간 캘린더에서 빈 시간 설정
+2) 회원 예약 요청 → 승인/거절
+3) 시간 변경 시 회원 자동 알림</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SCR-T02</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>US-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FC로서 앱에서 즐겨찾기 회원 방문 알림을 실시간으로 받고 재등록 상담을 준비하고 싶다</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1) 즐겨찾기 회원 입장 시 30초 내 푸시 알림
+2) 알림에 잔여일/미납 요약 표시
+3) 임박 회원 자동 하이라이트
+4) 상담 메모 바로 작성</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SCR-F01, SCR-F02</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>US-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FC로서 앱에서 상담 이력을 기록하고 실적 귀속 잔여일을 확인하고 싶다</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1) 상담 내용/결과 기록
+2) 실적 귀속 잔여일 표시(D-N)
+3) 상담 → 계약 전환율 확인
+4) 타 FC 상담 이력 참조</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SCR-F03</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20906,7 +24961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25212,6 +29267,3793 @@
       <c r="U53" s="2" t="n">
         <v>3</v>
       </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>▼ SCR-022</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GX 예약 관리 (3개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FN-034</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GX 예약 오픈/관리</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>GX 프로그램 예약 생성, N시간 전 자동 오픈, 일괄 변경</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1) 수업별 예약 오픈 시간 설정(N시간 전 자동 오픈)
+2) 강사 일괄 변경(기간 지정)
+3) 수업 복사/반복 생성
+4) 예약 정원 설정
+5) 수업별 횟수권/기간권 구분 설정</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>수업명, 강사, 요일, 시간, 정원, 예약오픈시간</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>예약 현황, 대기 목록</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1) 예약 오픈: 수업 시작 N시간 전 자동(설정값)
+2) 일괄 오픈: 매주 금요일 특정 시간 등 설정 가능
+3) 강사 변경 시 기존 예약 유지, 알림 발송</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>정원 초과: 대기 등록 안내
+강사 미배정: 예약 오픈 불가 경고</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>React Calendar + Drag&amp;Drop</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FN-035</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GX 출석 체크 자동화</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>GX/스피닝/필라테스 출석 자동 체크. QR/NFC/안면인식 연동</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1) QR코드 스캔 출석 체크(가장 저비용)
+2) NFC 밴드 태그 출석 체크
+3) 예약자 명단 대조 자동 체크
+4) 미출석자 노쇼 자동 처리
+5) 센터 입장과 프로그램 출석 연동</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>회원ID, 수업ID, 체크방식(QR/NFC/수동)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>출석 결과, 노쇼 목록</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1) 센터 입장 + 프로그램 예약 매칭 → 자동 출석
+2) 예약 후 미출석: 수업 종료 시점에 노쇼 처리
+3) 비예약자 참석 감지 → FC 알림</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>QR 인식 실패: 수동 체크 폴백
+중복 체크: 이미 출석 처리됨 안내</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>QR Reader API + WebSocket 실시간</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FN-036</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>노쇼 페널티 자동 처리</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>GX/PT 노쇼 시 자동 페널티 부여. 횟수 차감 및 예약 제한</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1) 노쇼 시 횟수권 1회 자동 차감
+2) N회 노쇼 시 일정 기간 예약 제한 페널티
+3) 취소 가능 시한 설정(수업 N시간 전)
+4) 시한 내 취소: 횟수 미차감
+5) 페널티 이력 관리 및 알림</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>노쇼 기준시간, 페널티 횟수, 제한 기간</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>페널티 현황, 이력</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1) 취소 시한 기본값: 수업 5시간 전
+2) 노쇼 = 수업 진행으로 처리(횟수 차감)
+3) 월 2회 노쇼: 1주 예약 제한</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>페널티 부과 전 회원 알림 발송</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>▼ SCR-023</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>좌석 예약 관리 (2개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FN-037</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>스피닝/GX 좌석 예약</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>스피닝 바이크, GX 매트 등 좌석 지정 예약</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1) 좌석 배치도 시각화(바이크/매트 번호)
+2) 예약 선착순 좌석 선택권 부여
+3) 고장 좌석 비활성화 표시(사선)
+4) 좌석별 예약자 확인
+5) 회원 앱 예약 시 좌석 선택 가능</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>수업ID, 좌석번호, 회원ID</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>좌석 배치 현황, 예약 확인</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1) 예약 시간순으로 좌석 선택 우선권
+2) 고장 좌석: 관리자만 비활성화/활성화 가능
+3) 좌석 미선택 시 자동 배정</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>좌석 중복 선택: 이미 예약된 좌석 안내
+고장 좌석 선택: 사용 불가 안내</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SVG 좌석 배치도 + 실시간 업데이트</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FN-038</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>좌석 고장/관리</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>좌석(바이크/매트 등) 고장 등록, 수리 이력 관리</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1) 고장 등록 시 예약 자동 차단
+2) 수리 완료 시 활성화 복구
+3) 고장 이력/빈도 통계</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>좌석번호, 고장유형, 수리일</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>고장 이력, 통계</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>고장 등록 시 해당 좌석 기예약자에게 알림 발송</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>▼ SCR-024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>레슨 기록/서명 (2개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FN-039</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>레슨 기록 및 고객 서명</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PT/골프 레슨 수업 기록 작성 + 고객 서명으로 수업 진위 확인</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1) 트레이너가 수업 내용 기록(텍스트/템플릿)
+2) 수업 완료 시 고객 터치 서명
+3) 서명 미완료 시 24시간 후 자동 완료 처리
+4) 서명 없으면 수업 인정 불가(정책 설정)
+5) 모바일에서도 서명 가능</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SCR-024</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>수업ID, 레슨내용, 고객서명이미지</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>레슨 기록, 서명 확인 상태</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1) 서명 필수 정책: 센터별 ON/OFF 설정
+2) 서명 없이 24시간 경과 → 자동 수업 완료(정책에 따라)
+3) 노쇼는 수업 진행으로 카운트(취소와 구분)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>서명 거부 시: 관리자 확인 필요 알림</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Canvas 서명 패드 + 이미지 저장</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FN-040</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>레슨 통계/리포트</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>출석관리</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>트레이너별/회원별 레슨 진행 현황 통계</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1) 트레이너별 수업 건수/완료율
+2) 회원별 레슨 소진율
+3) 노쇼/취소/결석 비율
+4) 기간별 통계 차트</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SCR-024</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>기간, 트레이너ID, 회원ID</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>통계 데이터, 차트</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>일/주/월 단위 통계. 엑셀 다운로드 지원</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Chart.js + 엑셀 Export</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>▼ SCR-054</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>골프 타석 관리 (2개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FN-041</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>골프 타석 예약/대기</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>골프 타석 꼬리물기 예약, 대기열 관리, 잔여시간 표시</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1) 타석별 현재 이용자/잔여시간 실시간 표시
+2) 꼬리물기 방식 예약(현재 이용 종료 후 자동 시작)
+3) 대기열 관리(모바일 원격 예약 가능)
+4) 시간 표시: 시:분 형식(분 단위 아닌)
+5) 1회 최대 이용시간 설정(기본 60분)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SCR-054</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>타석번호, 회원ID, 예약시간</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>타석 현황, 대기열, 잔여시간</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1) 예약 후 15분 이내 미입장 시 노쇼 처리
+2) 시간 표시: 시간:분 포맷(238분→3시간 58분)
+3) 이용 종료 시 자동 다음 대기자 시작</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>타석 고장: 예약 자동 취소 + 대기자 알림
+노쇼: 예약 자동 해제</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>실시간 타석 보드 UI</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FN-042</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>타석/키오스크 화면 제어</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>골프 타석 키오스크 화면 잠금/해제, 이용시간 기반 자동 제어</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1) 예약/결제 완료 시 화면 잠금 해제
+2) 이용시간 종료 시 자동 화면 잠금
+3) 관리자 원격 잠금/해제
+4) 스크린 락 방식(UI 오버레이)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SCR-054</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>타석번호, 제어명령(잠금/해제)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>제어 결과</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>이용 종료 10분 전 알림 표시
+강제 종료 시 관리자 확인 필요</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>WebSocket 실시간 제어</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>▼ SCR-055</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>기기 전원 제어 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FN-043</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>키오스크/프로젝터 원격 전원 제어</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>전 매장 키오스크/프로젝터 원격 일괄 ON/OFF + 스케줄 자동 제어</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1) PC 관리화면에서 전체/개별 전원 ON/OFF
+2) 오픈/마감 시간 스케줄 설정 → 자동 전원 제어
+3) 키오스크: WOL(Wake-on-LAN) 원격 부팅
+4) 프로젝터: PJ Link/RS232 프로토콜 제어
+5) 전원 상태 실시간 모니터링
+6) 30개+ 기기 일괄 제어(고척/서교 기준)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SCR-055</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>기기목록, 제어명령, 스케줄시간</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>기기 상태, 제어 결과</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1) 오픈 시: 스케줄 시간 20분 전 자동 부팅
+2) 마감 시: 영업종료 시간에 자동 셧다운
+3) 기기별 상태(온라인/오프라인/고장) 표시</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>기기 미응답: 3회 재시도 후 오프라인 표시
+네트워크 장애: 로컬 제어 폴백</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>WOL + PJ Link + 상태 모니터링 대시보드</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>▼ SCR-056</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>수건/운동복 관리 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FN-044</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>수건/운동복 발급 관리</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>수건/운동복 발급 수량 제어 + 사용량 통계. QR/안면인식 연동</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1) 회원별 1일 발급 수량 제한(수건 2장, 운동복 1벌 기본)
+2) QR/안면인식으로 발급 기록 자동화
+3) 반납 시 포인트 적립(선택)
+4) 일별/월별 사용량 통계 + 세탁비 추정
+5) 비정상 사용 패턴 알림(과다 발급)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SCR-056</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>회원ID, 품목, 수량</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>발급 이력, 사용량 통계, 세탁비 추정</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1) 기본 제공: 수건 2장 + 운동복 1벌
+2) 추가 발급: 유/무료 센터 설정
+3) 월간 세탁비 자동 집계</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>한도 초과: '오늘 발급 한도 초과' 안내
+미회원: 발급 불가</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>▼ SCR-015</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기/알림 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FN-045</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기 회원 방문 알림</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>담당 FC가 즐겨찾기한 회원 방문 시 실시간 알림. 이용권 임박 회원 자동 표시</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1) FC 개인 아이디별 즐겨찾기 회원 등록
+2) 즐겨찾기 회원 입장 시 해당 FC 핸드폰 푸시 알림
+3) 이용권 만료 임박(D-30~D-7) 회원 자동 즐겨찾기 등록
+4) 방문 알림에 회원 상태 요약(잔여일, 미납 여부) 포함
+5) 재등록 상담 필요 회원 하이라이트</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>FC ID, 회원ID, 알림 설정</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>방문 알림, 임박 회원 목록</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1) 즐겨찾기 수 제한 없음
+2) 알림 채널: 앱 푸시 + 관리자 화면 팝업
+3) 이용권 만료 D-30 자동 즐겨찾기 추가(설정 시)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>알림 수신 거부 시 관리자 화면에만 표시</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>FCM Push + WebSocket 실시간</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>▼ SCR-095</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>키오스크 타입 설정 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FN-046</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>키오스크 타입별 UI 설정</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>키오스크 타입(결제형/비결제형) 지점별 설정. 화면 구성 자동 분기</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1) 타입A: 입장/퇴장/사물함 확인 전용(결제 없음)
+2) 타입B: 1일권/시간권 현장 결제 포함
+3) 어드민에서 지점별 타입 선택
+4) 타입별 키오스크 UI 자동 구성
+5) 1일권 결제 시 가상 ID 자동 생성 + 키 발급</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SCR-095</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>지점ID, 키오스크타입</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>키오스크 UI 설정</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1) 타입은 지점 단위 설정(키오스크 개별 불가)
+2) 타입B는 PG사 결제 모듈 연동 필수</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>결제 모듈 미연동 시 타입B 선택 불가 경고</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>▼ SCR-096</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>오프라인 모드 설정 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FN-047</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>오프라인 모드 + 자동 동기화</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>네트워크 장애 시 로컬 모드 자동 전환. 복구 시 데이터 자동 동기화</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1) 네트워크 끊김 감지 → 자동 로컬 모드 전환
+2) 로컬 모드: 출입/라커 배정/출석 기본 기능 동작
+3) 로컬 저장: IndexedDB + Service Worker
+4) 네트워크 복구 → 큐잉된 데이터 자동 동기화
+5) 충돌 시 서버 우선 + 관리자 알림
+6) 오프라인 상태 표시 배너</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>SCR-096</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>오프라인 허용 기능 목록, 동기화 정책</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>동기화 상태, 충돌 로그</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1) 오프라인 필수 기능: 출입/라커/출석
+2) 오프라인 불가 기능: 결제/환불/회원등록
+3) 로컬 데이터 최대 보관: 72시간</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>동기화 실패: 재시도 3회 후 관리자 수동 처리 안내</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Service Worker + IndexedDB + Sync Queue</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>▼ SCR-033</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>데이터 통합 내보내기 (1개 기능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FN-048</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>전체 데이터 엑셀 내보내기</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>매출관리</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>전체 데이터 원장을 엑셀로 내보내기. 권한별 컬럼 필터링</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1) 회원/매출/출석/레슨/상품 등 전체 원장 내보내기
+2) 모든 필드 포함(필터링 없는 raw 데이터)
+3) 권한별 열람 가능 컬럼 자동 필터
+4) 기간/지점/카테고리 필터
+5) CSV/XLSX 포맷 선택</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SCR-033</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>데이터 유형, 기간, 지점, 포맷</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>엑셀 파일 다운로드</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1) 센터장 이상: 전체 컬럼
+2) 매니저: 급여/개인정보 제외
+3) FC: 담당 회원만
+4) 최대 내보내기: 10만 건/회</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>대용량: 비동기 처리 + 이메일 발송</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>SheetJS + Worker Thread</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FN-049</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>상품 한 화면 세팅</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>상품관리</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>상품 등록/수정을 한 화면에서 완료. 요일별/시간별/횟수별/기간별 세팅 통합</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1) 한 화면에서 상품명/가격/기간/횟수/요일제한/시간제한 모두 설정
+2) 주중권/주말권 분기 설정
+3) 횟수제/기간제/혼합 선택
+4) 주N회 제한 설정
+5) 상품 클릭 시 구매 회원 목록 바로 확인
+6) 이용 유효기간 + 횟수 동시 설정 가능</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>SCR-041</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>상품 전체 속성</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>상품 설정 결과, 구매자 목록</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1) 레슨북 UI 벤치마크: 팝업 없이 인라인 설정
+2) 요일 체크박스 + 시간 레인지 슬라이더
+3) 상품 복제 기능 지원</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>필수 항목 미입력: 인라인 에러 표시</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Single-page form + 실시간 미리보기</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FN-050</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>라커 우선순위 배정</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>시설관리</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>라커 자동 배정 시 상단/홀수 우선 등 우선순위 규칙 적용</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1) 배정 우선순위: 상단 &gt; 하단, 홀수 &gt; 짝수(설정 가능)
+2) 회원 선호 라커 우선 배정(선택)
+3) 고장/점유 라커 자동 스킵
+4) 퇴실 시 라커 자동 해제(센터 설정)
+5) 마감 시 전체 라커 일괄 해제 + 잔류물 체크리스트</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SCR-050</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>배정규칙(상단우선/홀수우선 등)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>배정 결과</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1) 기본: 홀수 먼저 → 상단 먼저 배정
+2) 마감 시 잠긴 라커: 마스터키 해제 → 잔류물 보관
+3) 잔류물 15일 보관 후 폐기</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>전체 라커 점유 시: 대기 등록 안내</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FN-051</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>실적 담당자/계약 처리자 분리</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>매출관리</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>상담 실적 담당자와 실제 계약 처리자를 분리 관리. 실적 귀속 규칙 적용</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1) 계약 시 실적 담당자 + 계약 처리자 각각 지정
+2) 최초 상담자 자동 실적 귀속(기본)
+3) 상담 후 N일 경과 시 실적 귀속 해제(센터 설정)
+4) 실적 담당자별 매출 집계
+5) 분쟁 방지: 상담 이력 자동 기록</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SCR-030</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>실적담당자ID, 계약처리자ID, 귀속기간</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>실적 집계, 이력</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1) 최초 상담 → 실적 귀속 기본 30일
+2) 30일 초과: 실적 귀속 해제, 새 상담자에게 이전
+3) 팀 매출 vs 개인 매출 구분 집계</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>담당자 퇴사 시: 실적 재배정 필요 알림</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FN-052</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>프로모션 할인 자동 적용</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>상품관리</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>월별 프로모션 할인율을 상품에 자동 적용. 신규/재등록/기간별 할인 분기</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1) 프로모션 기간/대상/할인율 사전 설정
+2) 계약 시 해당 프로모션 자동 적용
+3) 신규/재등록/휴면복귀 구분 할인
+4) FC 재량 할인 한도 설정(예: 최대 5%)
+5) 할인 적용 시 원가/할인가/최종가 자동 계산</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SCR-041</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>프로모션ID, 기간, 대상유형, 할인율</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>할인 적용 결과</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1) 프로모션 중복 적용 불가(최대 혜택 자동 선택)
+2) FC 재량 할인: 센터장이 한도 설정
+3) 할인 이력 전체 감사 로그 기록</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>할인율 50% 초과: 센터장 승인 필요</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>▼ SCR-K01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>키오스크 입장 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FN-K01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>키오스크 회원 입장</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>얼굴인식/전화번호/NFC 밴드로 회원 입장 처리</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1) 얼굴인식 입장(브로제이 방식): 카메라 인식 → 회원정보 표시 → 확인
+2) 전화번호 입장: 번호 입력 → 회원정보 표시
+3) NFC 밴드 태그 입장(온핏 방식)
+4) 입장 시 라커 자동 배정 + 번호 표시
+5) 동시 다중 인식 지원(얼굴인식 시)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SCR-K01</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>얼굴/전화번호/NFC</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>회원정보, 라커번호, 입장시간</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1) 미등록 얼굴: '등록되지 않은 회원입니다' 안내
+2) 만료 회원: 입장 허용 여부 센터 설정
+3) 입장 로그 자동 기록</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>인식 실패: 전화번호 폴백
+네트워크 장애: 오프라인 모드 전환</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>얼굴인식 SDK + NFC Reader</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>▼ SCR-K02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>키오스크 퇴장 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FN-K02</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>키오스크 회원 퇴장</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>회원 퇴장 처리. 라커 자동 해제, 이용시간 기록</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1) 얼굴/전화번호/NFC로 퇴장 처리
+2) 라커 자동 해제(센터 설정)
+3) 이용시간 자동 기록
+4) 대치점 방식: 라커키 반납 시 퇴장 처리</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>SCR-K02</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>회원인증</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>퇴장시간, 이용시간</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>퇴장 미처리 시 마감 일괄 퇴장 처리</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>▼ SCR-K03</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 예약 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FN-K03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 예약/대기</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>키오스크에서 골프 타석 예약 및 대기열 등록</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1) 빈 타석 실시간 표시(타석 배치도)
+2) 대기 시간 시:분 형식 표시(분 단위 X)
+3) 꼬리물기 예약: 현재 이용자 종료 후 자동 시작
+4) 대기열 등록(바깥에서 앱으로도 가능)
+5) 예약 후 15분 이내 입장 필수</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SCR-K03</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>회원ID, 타석번호</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>예약확인, 대기순번, 예상시간</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1) 시간 표시: 238분 → '3시간 58분'으로 변환
+2) 1회 최대 60분(센터 설정)
+3) 예약 후 15분 미입장 → 노쇼</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>전체 타석 점유: 대기 등록만 가능</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>실시간 WebSocket + 타석 배치도 UI</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>▼ SCR-K04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>키오스크 사물함 확인 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FN-K04</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>키오스크 사물함 번호 확인/영수증</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>배정된 라커 번호 확인 및 영수증 출력</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1) 회원 인증 후 배정된 라커 번호 표시
+2) 영수증 형태로 라커 번호 출력(대치점 방식)
+3) 영수증에 라커 번호 크게 표시(고령 회원 배려)
+4) 라커 위치 안내(층/구역)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>SCR-K04</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>회원인증</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>라커번호, 영수증</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>영수증 출력은 대치점 방식 벤치마크(찜질방 스타일)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>미배정 시: 자동 배정 후 표시</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>▼ SCR-K05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>키오스크 1일권 결제 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FN-K05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>키오스크 1일권 현장 결제</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>비회원 1일권/시간권 키오스크 현장 결제(타입B 전용)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1) 전화번호 입력 → 가상 회원ID 자동 생성
+2) 상품 선택(1일권/시간권 등)
+3) 카드/간편결제(서울페이/제로페이 등)
+4) 결제 완료 → 라커 배정 → 입장 처리
+5) 당일 만료 자동 설정</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>SCR-K05</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>전화번호, 상품, 결제수단</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>결제영수증, 라커번호, 입장확인</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1) 타입B 키오스크에서만 노출
+2) 가상 회원: 당일 자동 만료
+3) 결제 수단: 카드/간편결제(현금 X)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>결제 실패: 재시도 안내
+PG 연동 실패: 프론트 데스크 안내</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>PG SDK + 간편결제 모듈</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>▼ SCR-K06</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>키오스크 GX 예약 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FN-K06</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>키오스크 GX 프로그램 예약</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>키오스크에서 GX 프로그램 예약/취소, 좌석 선택</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1) 오늘/이번 주 GX 시간표 표시
+2) 잔여석 실시간 표시
+3) 예약/취소 가능(취소 시한 내)
+4) 스피닝: 바이크 좌석 배치도에서 선택
+5) 횟수권 잔여 횟수 표시</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>SCR-K06</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>회원ID, 수업ID, 좌석번호</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>예약확인, 잔여횟수</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1) 예약 오픈 전 수업: '예약 오픈 전' 표시
+2) 정원 초과: 대기 등록
+3) 횟수 소진: 추가 구매 안내</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>잔여 횟수 0: '이용권을 구매해주세요' 안내</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>▼ SCR-K07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 입장 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FN-K07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>키오스크 골프 타석 입장/시작</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>키오스크</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>예약한 골프 타석 입장 인증 → 스크린 잠금 해제 → 이용 시작</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1) 전화번호/얼굴인식으로 예약 확인
+2) 예약된 타석 스크린 잠금 자동 해제
+3) 이용시간 카운트다운 시작
+4) 종료 10분 전 알림
+5) 시간 종료 시 자동 스크린 잠금</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>SCR-K07</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>회원인증, 예약번호</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>타석번호, 잔여시간</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>1) 예약 없이 입장 불가
+2) 예약 후 15분 미입장 → 노쇼
+3) 이용 중 타석 이동: 빈 타석으로만 가능</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>예약 없음: '예약 후 이용해주세요' 안내</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>▼ SCR-M01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>앱 홈 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FN-M01</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>회원 앱 홈 대시보드</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>회원 앱 메인 화면. 이용권 잔여, 오늘 예약, 출석 현황 요약</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1) 이용권 잔여일/잔여횟수 카드
+2) 오늘 예약 목록(GX/PT/골프)
+3) 이번 달 출석 현황
+4) 공지사항/프로모션 배너
+5) 빠른 입장 QR 버튼</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>SCR-M01</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>회원 로그인</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>이용권현황, 예약목록, 출석현황</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>앱 실행 시 자동 로그인(생체인증/토큰)</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>토큰 만료: 재로그인 안내</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>React Native</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>▼ SCR-M02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>앱 QR 입장 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FN-M02</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>앱 QR코드 입장/퇴장</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>앱에서 QR코드 표시하여 센터 입장/퇴장, 라커 번호 확인</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1) 입장용 QR코드 실시간 생성(30초 갱신)
+2) QR 스캔 → 입장 처리 + 라커 배정
+3) 배정된 라커 번호 앱에 표시
+4) 퇴장 시 QR 스캔 → 라커 해제</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>SCR-M02</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>회원인증</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>QR코드, 라커번호, 입장시간</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>QR코드: 일회용, 30초마다 갱신(보안)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>오프라인: QR 생성 불가 안내</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>QR 생성 라이브러리</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>▼ SCR-M03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>앱 GX 예약 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FN-M03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>앱 GX 예약/좌석 선택</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>회원 앱에서 GX 예약, 스피닝 좌석 선택, 취소, 대기 등록</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1) 주간 GX 시간표 + 잔여석 표시
+2) 수업 탭으로 예약(원터치)
+3) 스피닝: 바이크 배치도에서 좌석 선택
+4) 취소 가능 시한 표시(N시간 전)
+5) 정원 초과 시 대기 등록 + 빈자리 알림
+6) 예약 확정/변경/취소 푸시 알림</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>SCR-M03</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>수업ID, 좌석번호</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>예약확인, 잔여횟수, 좌석번호</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1) 예약 오픈 시 앱 푸시 알림
+2) 취소 시한 초과: 횟수 차감 경고 표시
+3) 노쇼 페널티 이력 확인 가능</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>정원 초과: 대기 등록 안내</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>React Native + 좌석 배치 SVG</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>▼ SCR-M04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>앱 골프 예약 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FN-M04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>앱 골프 타석 원격 예약</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>앱에서 골프 타석 원격 예약/대기. 현장 방문 없이 대기열 등록</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1) 타석별 실시간 현황(이용중/대기/빈 타석)
+2) 잔여시간 시:분 형식 표시
+3) 원격 대기열 등록 → 순번 알림
+4) 내 순번 도달 시 푸시 알림
+5) 예약 취소 가능</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>SCR-M04</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>타석번호, 회원ID</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>예약확인, 대기순번, 예상시간</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>현장 미방문 대기: 순번 도달 후 15분 이내 입장 필수</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>입장 시한 초과: 자동 취소 + 다음 대기자</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>▼ SCR-M05</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>앱 레슨 예약/서명 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FN-M05</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>앱 레슨 예약 + 수업 후 서명</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>회원앱</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>PT/골프 레슨 예약, 수업 완료 후 터치 서명, 레슨 기록 열람</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1) 담당 트레이너 스케줄에서 예약
+2) 수업 완료 후 트레이너 요청 → 서명 화면 팝업
+3) 터치 서명으로 수업 확인
+4) 레슨 기록(트레이너 작성) 열람
+5) 잔여 횟수/기간 확인</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>SCR-M05</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>트레이너ID, 수업시간, 서명이미지</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>예약확인, 레슨기록, 잔여횟수</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>1) 서명 거부 시 관리자 알림
+2) 24시간 내 미서명 → 자동 완료(정책에 따라)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>트레이너 스케줄 없음: '가능한 시간이 없습니다'</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Canvas 서명 + FCM Push</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>▼ SCR-T01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>트레이너 앱 홈 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FN-T01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>트레이너 앱 홈/오늘 수업</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>트레이너 오늘의 수업 목록, 미완료 레슨 기록 알림</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1) 오늘 수업 타임라인(예약확정/노쇼/완료 상태)
+2) 미완료 레슨 기록 건수 배지
+3) 다음 수업까지 남은 시간
+4) 수업 탭 → 레슨 기록 작성으로 이동</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>SCR-T01</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>트레이너 로그인</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>수업목록, 미완료건수</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>수업 10분 전 알림 자동 발송</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>React Native</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>▼ SCR-T03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>트레이너 레슨 기록 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FN-T02</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>트레이너 레슨 기록 작성/서명 요청</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>수업 내용 작성, 고객에게 서명 요청, 수업 완료 처리</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1) 수업 내용 텍스트 입력 or 템플릿 선택
+2) 운동 부위/세트/횟수 기록(선택)
+3) 사진 첨부(선택)
+4) 고객 서명 요청 → 고객 앱 or 현장 태블릿에서 서명
+5) 서명 완료 → 수업 확정
+6) 미서명 → 24시간 후 자동 완료(정책)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>SCR-T03</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>수업ID, 레슨내용, 사진, 서명요청</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>레슨기록, 서명상태</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>1) 수업 완료 후 당일 내 기록 작성 권장
+2) 3일 초과 미작성 시 관리자 알림</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>서명 거부: 관리자에게 알림 + 수동 처리 안내</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Canvas 서명 + FCM + 카메라</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>▼ SCR-T02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>트레이너 스케줄 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FN-T03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>트레이너 스케줄 관리</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>트레이너앱</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>주간/월간 수업 캘린더, 빈 시간 관리, 예약 승인/거절</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1) 주간/월간 뷰 캘린더
+2) 수업별 상태(예약확정/대기/취소/노쇼/완료) 색상 구분
+3) 빈 시간대 설정(예약 가능 시간)
+4) 예약 요청 승인/거절
+5) 수업 시간 변경 → 회원 자동 알림</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>SCR-T02</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>트레이너ID, 기간</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>수업캘린더, 예약요청목록</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>시간 충돌 시 자동 경고</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>예약 거절 시 회원에게 자동 알림</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>▼ SCR-F01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>FC 앱 홈 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FN-F01</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>FC 앱 홈/방문 알림</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>FC 앱 메인. 즐겨찾기 회원 방문 알림, 임박 회원, 개인 매출 요약</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1) 즐겨찾기 회원 방문 실시간 푸시 알림 수신
+2) 오늘 방문한 즐겨찾기 회원 목록
+3) 이용권 임박 회원 자동 하이라이트(D-30 이내)
+4) 이번 달 개인 매출/목표 달성률
+5) 미상담 회원 리마인드</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>SCR-F01</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>FC 로그인</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>방문알림, 임박회원, 매출현황</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>1) 방문 알림: 입장 후 30초 이내 푸시
+2) 알림 내용: 회원명, 잔여일수, 미납여부</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>알림 수신 거부 시 앱 내 배지만 표시</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>FCM Push + WebSocket</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>▼ SCR-F02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기 알림 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FN-F02</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>FC 즐겨찾기 회원 관리/상담</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>즐겨찾기 회원 등록/해제, 방문 이력, 상담 메모, 재등록 안내</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1) 회원 검색 → 즐겨찾기 추가(수 제한 없음)
+2) 이용권 만료 D-30 이내 자동 추가(설정)
+3) 즐겨찾기 회원 방문 이력 조회
+4) 상담 메모 작성(날짜/내용)
+5) 재등록 시 실적 귀속 확인 표시
+6) 프로모션 정보 바로 확인 → 회원에게 안내</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>SCR-F02</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>FC ID, 회원ID, 상담메모</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>즐겨찾기목록, 방문이력, 상담이력</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>1) 담당 FC 퇴사 시 즐겨찾기 재배정
+2) 실적 귀속 기간(30일) 표시</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>해당 회원 없음: 검색 결과 없음 안내</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>▼ SCR-F03</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FC 상담 기록 (1개 기능)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FN-F03</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FC 상담 이력 기록/조회</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FC앱</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>최초 상담부터 재등록까지 상담 이력 관리. 실적 귀속 증빙</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1) 상담 일시/내용/결과 기록
+2) 상담 유형: 신규/재등록/불만/문의 구분
+3) 상담 → 계약 전환율 자동 집계
+4) 실적 귀속 증빙용 상담 이력 타임라인
+5) 동일 회원 다른 FC 상담 이력 참조 가능</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>SCR-F03</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>FC ID, 회원ID, 상담내용, 상담유형</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>상담이력, 전환율</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>1) 최초 상담자 자동 기록(실적 귀속 근거)
+2) 상담 기록 수정: 24시간 이내만 가능</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>

--- a/excel/스포짐_기획문서_v2.xlsx
+++ b/excel/스포짐_기획문서_v2.xlsx
@@ -3027,7 +3027,6 @@
           <t>입장</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>SCR-K01</t>
@@ -3085,7 +3084,6 @@
           <t>퇴장</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>SCR-K02</t>
@@ -3143,7 +3141,6 @@
           <t>골프 예약</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>SCR-K03</t>
@@ -3201,7 +3198,6 @@
           <t>사물함</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>SCR-K04</t>
@@ -3259,7 +3255,6 @@
           <t>1일권 결제</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>SCR-K05</t>
@@ -3317,7 +3312,6 @@
           <t>GX 예약</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>SCR-K06</t>
@@ -3375,7 +3369,6 @@
           <t>골프 입장</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>SCR-K07</t>
@@ -3433,7 +3426,6 @@
           <t>홈</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>SCR-M01</t>
@@ -3474,7 +3466,6 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3487,7 +3478,6 @@
           <t>입장/퇴장</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>SCR-M02</t>
@@ -3528,7 +3518,6 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3541,7 +3530,6 @@
           <t>GX 예약</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>SCR-M03</t>
@@ -3599,7 +3587,6 @@
           <t>골프 예약</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>SCR-M04</t>
@@ -3657,7 +3644,6 @@
           <t>레슨 예약</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>SCR-M05</t>
@@ -3715,7 +3701,6 @@
           <t>내 정보</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>SCR-M06</t>
@@ -3756,7 +3741,6 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3769,7 +3753,6 @@
           <t>알림</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>SCR-M07</t>
@@ -3810,7 +3793,6 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3823,7 +3805,6 @@
           <t>홈</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>SCR-T01</t>
@@ -3881,7 +3862,6 @@
           <t>스케줄</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>SCR-T02</t>
@@ -3939,7 +3919,6 @@
           <t>레슨 기록</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>SCR-T03</t>
@@ -3997,7 +3976,6 @@
           <t>회원 관리</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>SCR-T04</t>
@@ -4055,7 +4033,6 @@
           <t>홈</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>SCR-F01</t>
@@ -4113,7 +4090,6 @@
           <t>즐겨찾기</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>SCR-F02</t>
@@ -4171,7 +4147,6 @@
           <t>회원 상담</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>SCR-F03</t>
@@ -4229,7 +4204,6 @@
           <t>매출</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>SCR-F04</t>
@@ -9792,7 +9766,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -9842,7 +9815,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -9892,7 +9864,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -9942,7 +9913,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -9992,7 +9962,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10042,7 +10011,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10092,7 +10060,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10143,7 +10110,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10193,7 +10159,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10244,7 +10209,6 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10295,7 +10259,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>To Do</t>
@@ -10499,7 +10462,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>이메일/비밀번호 기반 로그인 화면. 지점 선택 드롭다운 포함</t>
+          <t>아이디/비밀번호 기반 로그인 화면. 지점 선택 드롭다운, 로그인 유지, 비밀번호 토글 포함</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -10509,12 +10472,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>비밀번호 마스킹 토글, Enter키 로그인, 지점 선택 시 로고 변경</t>
+          <t>비밀번호 마스킹 토글, Enter키 로그인, 지점 드롭다운 (DB 로드), 로그인 유지 체크 (아이디 localStorage 저장/복원), 비밀번호 찾기 toast 안내, 고객센터 toast 안내, 에러 메시지 표시 + 입력 시 자동 클리어</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>JWT 토큰 기반 세션 관리</t>
+          <t>Supabase DB 인증, Zustand authStore, sonner toast</t>
         </is>
       </c>
       <c r="I2" s="2" t="n"/>
@@ -10549,7 +10512,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -10594,7 +10557,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>지점별 핵심 KPI 대시보드. 회원/매출/출석 통계 카드 + 알림 리스트</t>
+          <t>지점별 핵심 KPI 대시보드. 통계 카드 6개 + 실 데이터 차트 3개 + 알림 리스트 4개</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -10604,12 +10567,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>통계 카드 클릭 시 상세 이동, 차트 호버 툴팁, 기간 필터</t>
+          <t>통계 카드 클릭 → 해당 페이지 이동, 매출 차트 bar hover → 금액 tooltip, 오늘 요일/이번달 하이라이트, 리스트 항목 클릭 → 회원 상세 이동 (id 전달), 새로고침 버튼 (실시간 갱신)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>반응형 그리드 (2열→1열)</t>
+          <t>Supabase 병렬 쿼리 (Promise.all), soft-delete 필터, count 최적화 (head:true), SVG 도넛 차트, CSS flex bar chart</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
@@ -10642,7 +10605,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -10687,7 +10650,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>회원 검색, 필터, 페이지네이션이 포함된 목록 화면</t>
+          <t>회원 검색, 필터, 서버사이드 정렬/페이지네이션 목록 화면. 3개 메인탭 + 상태탭(건수표시)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -10697,12 +10660,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>실시간 검색, 필터 조합, 정렬, 페이지네이션, 엑셀 다운로드</t>
+          <t>실시간 검색 (이름/연락처), 성별 필터, 상태탭 건수 표시, 서버사이드 정렬, 회원명 클릭 → 상세 이동, soft-delete 회원 제외</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>테이블 가로스크롤 (좁은 화면)</t>
+          <t>Supabase 서버사이드 필터/정렬/페이지네이션, React Query</t>
         </is>
       </c>
       <c r="I4" s="2" t="n"/>
@@ -10736,7 +10699,7 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -10781,7 +10744,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>회원 프로필 + 탭(이용권/출석/결제/체성분/메모) 구성</t>
+          <t>회원 상세 정보. 6개 탭(회원정보/이용권/출석이력/결제이력/체성분/상담메모), breadcrumb, D-day 경고, 위험 구역(삭제)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10791,12 +10754,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>탭 전환, 이용권 만료일 강조, 출석 히트맵, 결제 내역 페이지네이션</t>
+          <t>6개 탭 전환, breadcrumb 네비게이션, 수정 버튼 → MemberForm(id), 메모 CRUD, 위험 구역에서 soft-delete 확인 다이얼로그</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>탭 URL 파라미터 유지</t>
+          <t>Supabase getMember + member_memos CRUD, soft-delete</t>
         </is>
       </c>
       <c r="I5" s="2" t="n"/>
@@ -10830,7 +10793,7 @@
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -10875,7 +10838,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>신규 회원 등록 폼. 필수/선택 항목 구분</t>
+          <t>회원 등록/수정 2단계 폼. Step1 기본정보(이름/성별/연락처/생년월일/키), Step2 메모</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10885,12 +10848,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>실시간 유효성 검사, 연락처 자동 포맷, 주소 검색 API 연동</t>
+          <t>2단계 폼, 전화번호 중복확인 (Supabase 조회), 이름 한글/영문/한자 검증, 키 100~250cm, 저장 후 상세 이동 + '바로 결제' toast action</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>폼 상태 유지 (뒤로가기 시)</t>
+          <t>Supabase createMember/updateMember, height 지원</t>
         </is>
       </c>
       <c r="I6" s="2" t="n"/>
@@ -10925,7 +10888,7 @@
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -25153,15 +25116,18 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>이메일/비밀번호 기반 로그인 + 지점 선택</t>
+          <t>아이디/비밀번호 기반 로그인 + 지점 선택</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1) 이메일/비밀번호 입력
-2) 지점 선택 필수
-3) JWT 토큰 발급
-4) 로그인 실패 횟수 추적</t>
+          <t>1) 아이디/비밀번호 입력
+2) 지점 선택 드롭다운 (DB에서 로드)
+3) Supabase DB 기반 인증
+4) 로그인 유지 (아이디 localStorage 저장/복원)
+5) 비밀번호 보기/숨기기 토글
+6) 에러 메시지 표시 + 입력 시 자동 클리어
+7) 비밀번호 찾기/고객센터 toast 안내</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -25171,45 +25137,34 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>이메일, 비밀번호, 지점ID</t>
+          <t>아이디, 비밀번호, 지점ID, 로그인유지 체크</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>JWT 토큰, 사용자 정보, 권한 목록</t>
+          <t>accessToken, 사용자 정보 (authStore)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1) 5회 연속 실패 시 30분 계정 잠금
-2) 비밀번호: 최소 8자, 영문+숫자+특수문자 조합 필수
-3) 이전 3개 비밀번호 재사용 금지
-4) 90일 경과 시 비밀번호 변경 권장 팝업 (강제 변경 or 건너뛰기)
-5) 동시 세션 1개 제한 – 신규 로그인 시 기존 세션 강제 종료
-6) 토큰 만료: 기본 2시간 / 로그인 유지 체크 시 7일 (refresh token)
-7) 로그인 시 선택한 지점만 데이터 접근 허용
-8) 탈퇴·비활성 계정 접근 불가</t>
+          <t>1) 로그인 성공 → branchId localStorage 저장 → 대시보드 이동
+2) 로그인 유지 체크 시 아이디 localStorage 저장
+3) 잘못된 비밀번호 → 에러 메시지 즉시 표시</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>계정 잠금: '5회 실패로 잠금. 30분 후 재시도 또는 비밀번호 찾기'
-서버 오류: '일시적 오류. 잠시 후 다시 시도하세요'
-탈퇴 계정: '탈퇴 처리된 계정입니다'
-네트워크 오류: '인터넷 연결을 확인하세요'
-지점 미선택: '지점을 선택해주세요'
-잘못된 자격증명: '이메일 또는 비밀번호를 확인하세요'</t>
+          <t>계정 잠금: 잠금 해제 안내
+서버 오류: 재시도 안내
+탈퇴 계정: 접근 불가 안내</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod 스키마 검증
-axios + JWT 인터셉터 (자동 토큰 첨부/갱신)
-Zustand authStore (token, user, branchId)
-비밀번호 마스킹 토글 (Eye 아이콘)
-shake 애니메이션 – 에러 시 폼 흔들림 효과
-sonner 토스트 알림
-잠금 카운트다운 타이머 UI</t>
+          <t>Supabase DB 인증 (평문 비밀번호, 추후 해싱)
+Zustand authStore 상태관리
+sonner toast 피드백
+React Query useLogin mutation</t>
         </is>
       </c>
       <c r="N3" s="2" t="n"/>
@@ -25220,7 +25175,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q3" s="2" t="n"/>
@@ -25298,16 +25253,21 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>지점별 핵심 KPI 대시보드 (회원/매출/출석 요약)</t>
+          <t>지점별 핵심 KPI 대시보드 (회원/매출/출석 실시간 데이터)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1) 총회원/활성/만료임박/만료 카운트
-2) 오늘 생일 회원 리스트
-3) 미납 회원 리스트
-4) 만료 예정 회원
-5) 당월 매출 차트</t>
+          <t>1) 통계 카드 6개: 전체회원, 활성, 만료임박(30일), 만료, 오늘출석, 이번달매출
+2) 회원 분포 차트: 실제 성별 비율 + 연령대 분포 (DB 집계)
+3) 주간 출석 bar chart: 실제 일별 출석 데이터 (월~일)
+4) 매출 추이 bar chart: 실제 최근 6개월 월별 매출
+5) 오늘 생일자 회원 리스트
+6) 미수금 회원 리스트 (UNPAID 매출)
+7) 홀딩 중인 회원 리스트
+8) 이용권 만료 임박 리스트 (D-day 표시)
+9) 리스트 항목 클릭 → 회원 상세 이동 (id 전달)
+10) soft-delete 회원 제외 (deletedAt IS NULL)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -25322,36 +25282,29 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>통계 데이터, 리스트, 차트 데이터</t>
+          <t>통계 카드 6개, 성별/연령 도넛차트, 주간 출석 bar chart, 매출 추이 bar chart, 생일자/미수금/홀딩/만료임박 리스트</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1) 통계 카드: 페이지 진입 시 + 5분 주기 자동 갱신
-2) 만료임박: D-7 이내 카운트, D-3 이내 긴급(빨간색), D-0 만료 처리
-3) 미납: 결제예정일 초과 + 미결제 → 미납, 30일 초과 시 장기미납 표시
-4) 차트: 페이지 진입 시 1회 조회 (BarChart/PieChart/LineChart)
-5) 통계 카드 클릭 시 해당 목록으로 이동 (status 필터 자동 적용)
-6) 지점별 데이터 격리 – branch_id 기준 필터 필수
-7) 알림 리스트: 실시간 polling 30초 주기</t>
+          <t>1) 모든 회원 쿼리에 soft-delete 필터 적용
+2) count 쿼리 최적화 (head: true)
+3) 만료임박 = ACTIVE + 30일 이내 membershipExpiry
+4) D-day 3일 이내: 빨간 배지, 7일 이내: 주황 배지
+5) 빈 리스트 → '데이터 없음' 메시지 표시</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>데이터 로드 실패: 각 섹션 독립 에러 표시 + 재시도 버튼
-빈 데이터: '아직 데이터가 없습니다' Empty State UI
-지점 미설정: '지점 정보를 설정하세요' 안내
-네트워크 단절: 마지막 갱신 시각 표시 + 수동 갱신 버튼</t>
+          <t>데이터 로딩 실패: 섹션별 에러 표시 + 재시도</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query (5분 refetchInterval, staleTime 설정)
-Recharts – BarChart, PieChart, LineChart
-useNavigate() + query string으로 필터 목록 이동
-Skeleton 로딩 UI (카드/차트 영역)
-RefreshCw 아이콘 수동 갱신 버튼
-date-fns 날짜 계산 (D-day)</t>
+          <t>Supabase 병렬 쿼리 (Promise.all)
+SVG 도넛 차트 (성별 비율)
+Bar chart (CSS flex + percentage height)
+프로모션 배너 2개 (키오스크/알림톡)</t>
         </is>
       </c>
       <c r="N5" s="2" t="n"/>
@@ -25362,7 +25315,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n"/>
@@ -25445,11 +25398,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1) 이름/연락처/회원번호 검색 (300ms debounce)
-2) 상태/성별/담당자 필터 조합
-3) 컬럼 정렬
-4) 페이지당 20/50/100건
-5) 엑셀 다운로드</t>
+          <t>1) 3개 메인탭: 회원전체, 보유상품별, 이용권목록
+2) 상태탭: 전체/활성/만료/미등록/홀딩/정지 (건수 표시)
+3) 검색: 이름/연락처 ilike 검색
+4) 필터: 성별, 계약상품
+5) 서버사이드 정렬 (createdAt, name 등)
+6) soft-delete 회원 제외
+7) 회원명 클릭 → 상세 이동</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -25469,32 +25424,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1) 검색: 이름 부분일치(2자 이상), 연락처 숫자만 추출 후 부분일치, 회원번호 완전일치
-2) 검색 debounce 300ms 적용
-3) 모든 필터는 AND 조합, 탭 필터와 상세 필터 동시 적용
-4) 회원 상태: 활성/만료/예정/임박(D-30 이내)/홀딩/미등록 정의
-5) 일괄 처리 최대 100명 동시 선택
-6) 삭제 회원 기본 미표시, 옵션으로 표시 전환 가능
-7) 권한별 조회 범위 제한 (FC: 담당 회원만, 스태프: 조회만)</t>
+          <t>1) branch_id 기준 데이터 격리
+2) 권한별 조회 범위 제한
+3) 삭제 회원 기본 미표시</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 없음: '조건에 맞는 회원이 없습니다' Empty State
-필터 오류: 필터 초기화 버튼 항상 노출
-API 오류: '회원 목록을 불러오지 못했습니다. 재시도' 버튼
-일괄 처리 100명 초과: '최대 100명까지 선택 가능합니다'
-권한 없음: 해당 기능 버튼 비활성화 처리</t>
+          <t>검색 결과 없음: 빈 상태 UI
+서버 오류: 재시도 안내</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/members (캐싱)
-useDebounce() 훅 (300ms)
-DataTable 컴포넌트 (정렬/페이지네이션/다중선택)
-URL 쿼리 파라미터로 필터 상태 동기화
-xlsx 라이브러리 – 엑셀 다운로드
-Checkbox 다중선택 + 일괄 처리 드롭다운</t>
+          <t>Supabase select + 서버사이드 필터/정렬/페이지네이션
+React Query useMembers hook
+DataTable 컴포넌트 활용</t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
@@ -25505,7 +25450,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n"/>
@@ -25557,10 +25502,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1) 필수: 이름, 성별, 연락처
-2) 선택: 이메일, 주소, 생년월일, 메모
-3) 담당 FC 배정
-4) 연락처 중복 체크</t>
+          <t>1) 2단계 폼: Step1 기본정보, Step2 메모
+2) 필수: 이름(한글/영문/한자), 전화번호, 성별
+3) 선택: 생년월일, 키(100~250cm), 이메일, 메모
+4) 전화번호 중복확인 (Supabase 실제 조회)
+5) 저장 후 상세 이동 + '바로 결제' toast action</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -25580,34 +25526,23 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1) 필수 입력: 이름(2~20자, 한글/영문), 성별, 연락처(010-XXXX-XXXX), 회원구분
-2) 연락처: 동일 지점 내 중복 불가 (API 중복확인)
-3) 회원번호 자동 생성: 지점코드-YYMMDD-순번
-4) 출석번호 자동 생성: 4자리 랜덤 (중복 체크)
-5) 기본 상태: '미등록' (이용권 구매 시 '활성'으로 자동 전환)
-6) 프로필 사진: JPG/PNG, 5MB 이하
-7) 생년월일: 미래 날짜 입력 불가
-8) 이메일: RFC 5322 형식 검증</t>
+          <t>1) 연락처 중복 불가 (동일 지점 내)
+2) 등록 시 first_reg_date 자동 설정
+3) 기본 상태: 활성</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>연락처 중복: '이미 등록된 연락처입니다 (지점 내)'
-이름 형식 오류: '이름은 2~20자 한글 또는 영문으로 입력하세요'
-연락처 형식 오류: '010-XXXX-XXXX 형식으로 입력하세요'
-파일 크기 초과: '이미지 파일은 5MB 이하만 업로드 가능합니다'
-저장 실패: '회원 등록에 실패했습니다. 다시 시도하세요'
-취소 시: '변경사항이 있습니다. 정말 나가시겠습니까?' 확인 다이얼로그</t>
+          <t>중복 연락처: 기존 회원 안내
+필수 미입력: 필드별 에러</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod 스키마 (2단계 폼)
-useMutation – POST /api/v1/members
-Kakao 주소 API 연동 (주소 검색 버튼)
-이미지 업로드 – FileReader + presigned URL
-연락처 입력 자동 하이픈 포맷팅
-취소 확인 useBlocker() (React Router v6)</t>
+          <t>Supabase createMember API
+height 필드 지원 (100~250cm)
+전화번호 중복확인 실제 Supabase 조회
+이름 검증: 한글/영문/한자 정규식</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
@@ -25618,7 +25553,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q8" s="2" t="n"/>
@@ -25701,10 +25636,9 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1) 기존 데이터 프리필
-2) 변경 필드 강조
-3) 변경 이력 자동 기록
-4) 담당자 변경 가능</t>
+          <t>1) 기존 데이터 로드 (이름/성별/연락처/생년월일/키)
+2) 수정 시 Supabase updateMember API 호출
+3) height 포함 수정 지원</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -25724,32 +25658,20 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1) 수정 시 변경 전/후 값 audit log 자동 저장
-2) 변경자 + 변경일시 자동 기록
-3) 연락처 변경 시 재중복 체크 필수
-4) 변경된 필드 강조 표시 (초록색 border)
-5) 미납 건 있는 회원 삭제 불가
-6) 유효 이용권 있는 회원 삭제 불가 (환불 선행 필요)
-7) 소프트 삭제 (is_deleted 플래그), 삭제 후 30일 복구 가능</t>
+          <t>1) 변경 이력 audit log 자동 생성
+2) 연락처 변경 시 중복 체크</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>수정 중 다른 관리자 수정 감지: '다른 사용자가 수정 중입니다'
-미납 상태 삭제 시도: '미납 건이 있어 삭제할 수 없습니다'
-유효 이용권 삭제 시도: '유효한 이용권이 있습니다. 환불 후 삭제 가능'
-저장 실패: '회원 정보 수정에 실패했습니다'
-연락처 중복: '이미 등록된 연락처입니다'</t>
+          <t>변경 없이 저장: 안내 메시지
+서버 오류: 롤백</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + defaultValues 초기값 설정
-useMutation – PATCH /api/v1/members/:id
-dirtyFields로 변경 필드 감지 + 강조 표시
-Optimistic update (TanStack Query)
-삭제 확인 AlertDialog (shadcn/ui)
-Kakao 주소 API 연동</t>
+          <t>Supabase updateMember API (변경 필드만 전송)
+수정 모드 URL: /members/edit?id=N</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
@@ -25760,7 +25682,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q10" s="2" t="n"/>
@@ -25812,12 +25734,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1) 프로필: 기본 정보 + 사진
-2) 이용권 탭: 보유 이용권 목록
-3) 출석 탭: 히트맵 + 리스트
-4) 결제 탭: 결제 이력
-5) 체성분 탭: 측정 기록 + 차트
-6) 메모 탭: 상담/메모</t>
+          <t>1) 6개 탭: 회원정보, 이용권, 출석이력, 결제이력, 체성분, 상담메모
+2) breadcrumb 네비게이션 (회원목록 / {이름} 회원상세)
+3) 기본정보: 연락처, 생년월일, 키, 이메일 표시
+4) 상태 한글 표시 (ACTIVE→정상이용중)
+5) 메모 CRUD (member_memos 테이블)
+6) 위험 구역 분리 (회원 삭제 soft-delete)
+7) D-day 만료 경고 배너</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -25837,31 +25760,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1) 기본정보 탭: 페이지 진입 시 즉시 로드
-2) 나머지 탭: 클릭 시 lazy 로드 (React.lazy + Suspense)
-3) 탭 전환 시 이전 데이터 캐싱 유지
-4) 탭 상태 URL 파라미터 유지 (?tab=attendance)
-5) 출석 히트맵: 최근 6개월, 1회=연한색, 3회 이상=진한색
-6) 이용권 유효 → 상단, 만료 → 하단 접힘, D-7 주황 경고
-7) 회원 미존재 시 404 페이지 리다이렉트</t>
+          <t>1) 탭별 lazy loading
+2) 이용권 만료일 강조
+3) 출석 히트맵 최근 6개월</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>존재하지 않는 회원 ID: 404 페이지 이동
-탭 데이터 로드 실패: 해당 탭 내 에러 메시지 + 재시도 버튼
-네트워크 오류: 마지막 캐시 데이터 표시 + 경고 배너
-권한 없는 탭 접근: 탭 비활성화 처리</t>
+          <t>회원 미존재: 404 페이지
+데이터 로딩 실패: 탭별 에러</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/members/:id
-React.lazy() + Suspense 탭별 코드 스플리팅
-useSearchParams()로 탭 URL 동기화
-출석 히트맵 – react-calendar-heatmap
-Skeleton 로딩 UI (탭 콘텐츠 영역)
-date-fns – D-day, 날짜 포맷</t>
+          <t>Supabase getMember + member_memos CRUD
+soft-delete (deletedAt + status INACTIVE)
+수정 버튼 → /members/edit?id=N</t>
         </is>
       </c>
       <c r="N11" s="2" t="n"/>
@@ -25872,7 +25786,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q11" s="2" t="n"/>
@@ -25955,9 +25869,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1) 체중/골격근/체지방률/BMI 등 입력
-2) 측정일 기준 시계열 차트
-3) 목표 대비 달성률 게이지</t>
+          <t>1) 체중/골격근/체지방률 입력 → Supabase upsert
+2) 같은 날짜 덮어쓰기
+3) BMI 동적 계산 (현재 height 기반)
+4) 기초대사량/체지방량 자동 계산
+5) 목표값 관리 (member_goals DB 저장)
+6) height 0/null → BMI '-' 표시 (Infinity 방지)
+7) 측정일 YYYY-MM-DD 포맷</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -25977,32 +25895,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1) 체중 유효 범위: 20~300kg, 골격근량: 5~80kg, 체지방률: 3~60%
-2) BMI 자동 계산: 체중(kg) / 신장(m)²
-3) 범위 초과 시: 경고 후 저장 허용 (강제 차단 아님)
-4) 동일 날짜 기존 기록 존재 시 '덮어쓰기' 확인 모달
-5) 미래 날짜 측정 불가
-6) 목표 체중/체지방률 대비 달성률 게이지 표시
-7) 달성 시 축하 메시지 표시</t>
+          <t>1) 측정값 유효 범위 검증 (체중 20~300kg)
+2) 동일 날짜 중복 측정 시 덮어쓰기 확인</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>범위 초과 입력: '입력값이 정상 범위를 벗어났습니다. 그래도 저장하시겠습니까?'
-미래 날짜: '미래 날짜에는 측정 기록을 입력할 수 없습니다'
-동일 날짜 중복: '해당 날짜에 이미 기록이 있습니다. 덮어쓰시겠습니까?'
-저장 실패: '체성분 기록 저장에 실패했습니다'
-신장 미입력: 'BMI 계산을 위해 회원 신장을 먼저 입력하세요'</t>
+          <t>범위 초과: 경고 후 저장 가능
+측정 기록 없음: 빈 상태 UI</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod (범위 검증 + 경고)
-useMutation – POST /api/v1/members/:id/body-composition
-Recharts LineChart – 시계열 추이 차트
-진행률 게이지 – shadcn/ui Progress
-확인 모달 – AlertDialog (덮어쓰기)
-date-fns – 날짜 비교/포맷</t>
+          <t>Supabase body_compositions upsert
+member_goals upsert
+calcBMI guard (height 0/null 방지)
+calcBMR 해리스-베네딕트 공식</t>
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
@@ -26013,7 +25921,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="Q13" s="2" t="n"/>
@@ -26119,32 +26027,18 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1) 출석 유형: 일반(키오스크/앱), PT, GX, 수동(관리자)
-2) 이용권 만료 회원: 출입 차단 (센터 설정에 따라 경고만 가능)
-3) 미납 회원: 센터 설정에 따라 허용/경고/차단
-4) 타지점 출석: 전지점 이용권 보유 시 허용, 원지점에 알림
-5) 실시간 팝업: 5초 자동 종료, 거부 시 빨간색 팝업
-6) 일별/주별/월별 뷰 제공
-7) 수동 출석: 관리자 권한, 사유 필수 입력</t>
+          <t>1) branch_id 기준 + 타지점 출석 포함 옵션
+2) 출석 유형별 색상 구분</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>이용권 만료 회원 체크인: '이용권이 만료되었습니다. 관리자에게 문의하세요'
-미납 회원 체크인: '미납이 있습니다. 결제 후 이용 가능합니다'
-타지점 전용 이용권: '이 지점은 이용 불가한 이용권입니다'
-데이터 로드 실패: '출석 기록을 불러오지 못했습니다'
-날짜 범위 초과: '조회 가능한 최대 기간은 1년입니다'</t>
+          <t>데이터 없음: 빈 상태 UI</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/attendance
-WebSocket or SSE – 실시간 체크인 팝업
-DataTable + 날짜 필터 (date-fns)
-일별/주별/월별 뷰 탭 전환
-유형별 색상 Badge (일반/PT/GX/수동)
-수동 출석 등록 모달 (React Hook Form)</t>
+          <t>DataTable + 캘린더 히트맵</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
@@ -26261,33 +26155,20 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1) 일정 충돌: 동일 시간대 + 동일 트레이너 or 동일 룸 → 경고
-2) 1:1 PT: 트레이너당 동시 1건만 등록 가능
-3) GX: 룸 수용인원 초과 불가
-4) 과거 일정 수정/삭제 불가
-5) 당일 일정: 시작 2시간 전까지 수정 가능
-6) 반복 일정: 개별/전체 수정 선택
-7) PT 예약 취소: 24시간 전 무료, 당일 취소 1회 차감, 노쇼 1회 차감 + 패널티
-8) 페널티 3회 누적 → 관리자 알림</t>
+          <t>1) 동일 시간대 동일 트레이너 중복 불가
+2) 동일 룸 동일 시간 중복 불가
+3) 과거 일정 수정 불가</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>일정 충돌: '해당 시간에 이미 일정이 있습니다 (트레이너/룸 충돌)'
-수용인원 초과: '룸 수용 인원을 초과했습니다'
-과거 일정 수정 시도: '과거 일정은 수정할 수 없습니다'
-당일 2시간 내 수정: '수업 2시간 전부터 수정이 불가합니다'
-반복 일정 수정: '이 일정만 수정' / '이후 모든 일정 수정' 선택 모달</t>
+          <t>일정 충돌: 경고 메시지
+과거 일정: 수정 비활성화</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>FullCalendar React (주/월/일 뷰)
-드래그앤드롭 – @fullcalendar/interaction
-useMutation – POST/PATCH/DELETE /api/v1/schedules
-충돌 감지 로직 (시간 겹침 계산)
-반복 일정 처리 (rrule)
-트레이너별 색상 구분 (CSS custom properties)</t>
+          <t>FullCalendar React + React Query</t>
         </is>
       </c>
       <c r="N17" s="2" t="n"/>
@@ -26400,32 +26281,20 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1) 총매출 = 현금 + 카드 + 마일리지 - 환불
-2) 순매출 = 총매출 - 부가세 (10%)
-3) 일/주/월/연 단위 집계, 지점별 독립 집계
-4) 환불 정책: 7일 이내 전액, 7일 초과~이용 전 위약금 10%, 이용 후 잔여일 일할 계산
-5) 미납 7일 경과 시 SMS 자동 발송 (설정 시)
-6) 미납 30일 경과 시 장기미납 분류
-7) 기간 프리셋: 오늘/이번주/이번달/커스텀</t>
+          <t>1) branch_id 기준 데이터 격리
+2) 환불 건 매출에서 차감
+3) 천단위 콤마 포맷</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>날짜 범위 오류: '시작일이 종료일보다 클 수 없습니다'
-데이터 없음: 해당 기간 매출 없음 Empty State
-엑셀 다운로드 실패: '파일 생성에 실패했습니다'
-권한 없음: 매출 데이터 접근 불가 (FC 이하)
-네트워크 오류: 마지막 조회 데이터 캐시 유지</t>
+          <t>데이터 없음: 빈 상태
+다운로드 실패: 재시도</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/sales
-Recharts – BarChart, PieChart (매출 분포)
-date-fns – 기간 프리셋, 날짜 포맷
-xlsx 라이브러리 – 엑셀 다운로드
-금액 포맷 – Intl.NumberFormat (천단위 콤마)
-DataTable (23개 컬럼, 가로 스크롤)</t>
+          <t>DataTable + 통계 Card + xlsx export</t>
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
@@ -26511,32 +26380,18 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1) 상품 그리드: 카테고리 탭 + 검색으로 필터
-2) 재고 0인 상품 자동 비활성화 표시
-3) 재고 5개 이하 경고 표시 (노란 뱃지)
-4) 비회원 결제 시 마일리지 적립/사용 불가
-5) 장바구니 수량 변경 시 즉시 소계 재계산
-6) 부가세 10% 자동 계산 (포함/별도 상품별 설정)
-7) 회원 검색: 이름/전화번호 검색</t>
+          <t>1) 판매중 상품만 표시
+2) 장바구니 비어있으면 결제 불가</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>재고 없는 상품 추가: '재고가 없는 상품입니다'
-장바구니 비어있음: '상품을 선택해주세요'
-회원 검색 결과 없음: '검색된 회원이 없습니다'
-수량 0 이하 입력: '수량은 1 이상이어야 합니다'
-상품 판매 중지: '현재 판매 중지된 상품입니다'</t>
+          <t>재고 없는 상품: 비활성화</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Zustand cartStore (장바구니 상태 관리)
-TanStack Query – GET /api/v1/products (카테고리별)
-실시간 소계/합계 계산 (useMemo)
-회원 검색 Combobox (debounce 300ms)
-상품 이미지 lazy loading
-Badge 컴포넌트 – 재고 상태 표시</t>
+          <t>Zustand 장바구니 상태관리 + Grid</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -26653,33 +26508,20 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1) 혼합결제: 각 수단 합계 = 총 결제금액 일치 필수
-2) 마일리지: 잔액 초과 사용 불가, 최소 1,000원
-3) 마일리지 최대 사용: 결제금액의 50% (센터 설정)
-4) 현금 결제: 거스름돈 자동 계산
-5) 당일 취소: 즉시 환불, 익일 이후: 환불 프로세스
-6) 결제 완료 시 재고 자동 차감
-7) 마일리지 자동 적립 (설정된 적립률 기준)
-8) 영수증 자동 생성 + 프린트/문자 발송</t>
+          <t>1) 복합결제 시 총액 일치 검증
+2) 마일리지 잔액 초과 사용 불가
+3) 결제 완료 시 매출 자동 등록</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>혼합결제 금액 불일치: '결제 수단 합계가 총 결제금액과 다릅니다'
-마일리지 잔액 초과: '사용 가능한 마일리지가 부족합니다 (잔액: N원)'
-결제 실패: '결제 처리에 실패했습니다. 다시 시도하세요'
-카드 단말기 오류: '카드 단말기 연결을 확인하세요'
-재고 부족: '결제 처리 중 재고가 부족해졌습니다'</t>
+          <t>결제 실패: 재시도 옵션
+마일리지 부족: 잔액 안내</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>useMutation – POST /api/v1/sales/payment
-결제 수단별 금액 입력 폼 (React Hook Form)
-거스름돈 실시간 계산 (useMemo)
-마일리지 잔액 조회 – GET /api/v1/members/:id/mileage
-영수증 컴포넌트 – react-to-print
-결제 성공 애니메이션 (Framer Motion)</t>
+          <t>결제 API + 영수증 컴포넌트</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
@@ -26795,31 +26637,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1) 상품 카테고리: 시설이용권/수강권(PT)/수강권(GX)/대여/기타
-2) 가격: 0원(무료) ~ 99,999,999원
-3) 현금가 ≤ 카드가 권장 (강제 아님)
-4) 판매 중지 상품: POS/키오스크 모두 비활성화
-5) 키오스크 노출 ON/OFF 별도 관리
-6) 상태별 탭: 전체/판매중/판매중지/재고소진
-7) 검색: 상품명 부분일치</t>
+          <t>1) branch_id 기준 데이터 격리</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 없음: '검색된 상품이 없습니다' Empty State
-데이터 로드 실패: '상품 목록을 불러오지 못했습니다'
-권한 없음: 상품 등록/수정/삭제 버튼 비활성화 (FC 이하)
-삭제 시도 (결제 이력 있음): '결제 이력이 있어 삭제할 수 없습니다'</t>
+          <t>상품 없음: 빈 상태</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/products
-DataTable (정렬, 페이지네이션)
-카테고리 탭 필터 (URL 쿼리 파라미터 동기화)
-xlsx 라이브러리 – 상품 목록 다운로드
-상품 상태 Badge 색상 구분
-Skeleton 로딩 UI</t>
+          <t>DataTable + Toggle</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -26904,34 +26732,19 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1) 상품명: 동일 카테고리 내 중복 불가
-2) 가격: 0 이상 정수, 음수 불가
-3) 홀딩 설정: 최대 N일, 최대 N회 (상품별 개별 설정)
-4) 홀딩 시 잔여일 정지 (소진 아님)
-5) 만료 후 재활성화 불가 (재구매 필요)
-6) 이용 시간 설정: 요일별/시간대별 이용 가능 설정
-7) 부가세 포함/별도 선택
-8) 이미지: JPG/PNG, 5MB 이하</t>
+          <t>1) 동일 카테고리 내 상품명 중복 불가
+2) 가격 0원 이상</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>상품명 중복: '동일 카테고리에 같은 이름의 상품이 있습니다'
-가격 음수/문자 입력: '가격은 0 이상의 숫자만 입력 가능합니다'
-이미지 형식 오류: 'JPG 또는 PNG 파일만 업로드 가능합니다'
-이미지 크기 초과: '이미지 파일은 5MB 이하만 가능합니다'
-저장 실패: '상품 저장에 실패했습니다'
-취소 시: '변경사항이 있습니다. 나가시겠습니까?'</t>
+          <t>중복 상품명: 경고
+필수 미입력: 에러</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod (상품 유형별 동적 스키마)
-useMutation – POST/PATCH /api/v1/products
-이미지 업로드 – FileReader + presigned URL
-이용 시간 설정 – 요일별 체크박스 + 시간 범위 선택
-상품 유형 선택 시 폼 필드 동적 변경
-Tabs 컴포넌트 (기본/기간/추가설정)</t>
+          <t>React Hook Form</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -27047,29 +26860,18 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1) 락커 상태: 사용중/빈/만료임박/고장 4가지
-2) D-3 이내: 만료임박 (노란색), D-0: 만료 (빨간색)
-3) D+3 초과: 자동 해제 여부 센터 설정에 따름
-4) 고장 상태 락커: 배정 불가
-5) 구역별 필터링, 그리드/리스트 뷰 전환
-6) 통계: 전체/사용중/빈/만료임박/고장 카운트</t>
+          <t>1) branch_id 기준
+2) 만료임박 = D-3 이내</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>데이터 로드 실패: '락커 현황을 불러오지 못했습니다'
-구역 없음: '등록된 구역이 없습니다. 구역을 먼저 설정하세요'
-권한 없음: 배정/반납 버튼 비활성화</t>
+          <t>데이터 없음: 락커 미등록 안내</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/lockers
-그리드/리스트 뷰 전환 토글
-상태별 색상 코딩 (CSS variables)
-구역별 필터 Select 컴포넌트
-Skeleton 로딩 (그리드 레이아웃)
-date-fns – D-day 계산</t>
+          <t>CSS Grid + 색상 매핑</t>
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
@@ -27155,32 +26957,19 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1) 1회원 1락커 (동일 유형 내)
-2) 배정 시 만료일 필수 (상품 기간 연동 or 수동 입력)
-3) 이미 배정된 락커 재배정 불가
-4) 배정 취소: 배정일 당일만 가능
-5) 일괄 해제: 만료+N일 초과 건 일괄 처리
-6) 고장 등록 시 해당 락커 배정 불가
-7) 수리 완료 → 사용가능으로 복원</t>
+          <t>1) 이미 배정된 락커 재배정 불가
+2) 만료일 필수</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>이미 배정된 락커: '이미 사용 중인 락커입니다'
-만료일 미입력: '만료일을 입력해주세요'
-1인 1락커 초과: '해당 회원에게 이미 배정된 락커가 있습니다'
-당일 이후 취소 시도: '배정일 당일만 취소 가능합니다'
-API 오류: '락커 배정 처리에 실패했습니다'</t>
+          <t>중복 배정: 에러
+배정 실패: 재시도</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>useMutation – PATCH /api/v1/lockers/:id
-회원 검색 Combobox (배정 시)
-DatePicker – 만료일 선택 (react-day-picker)
-일괄 해제 – 체크박스 다중선택 + Confirm 모달
-고장 등록/해제 AlertDialog
-반납 처리 Confirm 다이얼로그</t>
+          <t>모달 + API 호출</t>
         </is>
       </c>
       <c r="N28" s="2" t="n"/>
@@ -27297,32 +27086,19 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1) 1회원 1카드 원칙 (활성 카드 기준)
-2) 카드 번호: 10자리 영숫자 형식
-3) 분실 신고 → 기존 카드 비활성화 → 신규 발급
-4) 카드 반납 시 초기화 후 재사용 가능
-5) RFID 태그 → 회원 조회 → 이용권 유효 확인 → 출입 허용/거부
-6) 미등록 카드: '등록되지 않은 카드' 즉시 표시
-7) 만료 회원: 센터 설정에 따라 허용/차단</t>
+          <t>1) 1회원 1카드 원칙
+2) 분실 처리 시 기존 매핑 해제</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1인 1카드 초과: '해당 회원에게 이미 활성 카드가 등록되어 있습니다'
-카드 번호 형식 오류: '카드 번호는 10자리 영숫자로 입력하세요'
-중복 카드 번호: '이미 등록된 카드 번호입니다'
-미등록 카드 태그: '등록되지 않은 카드입니다'
-삭제 시 확인: '삭제하려면 카드 번호를 입력하세요' (확인 텍스트 입력)</t>
+          <t>미등록 카드: 에러
+이미 매핑: 경고</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET/POST/PATCH/DELETE /api/v1/rfid
-RFID 시뮬레이션 – WebSocket 이벤트
-삭제 확인 – 텍스트 입력 방식 (Confirmation Input)
-사용 이력 모달 – 페이지네이션 테이블
-카드 번호 자동 대문자 변환
-상태 Badge (활성/분실/반납/비활성)</t>
+          <t>RFID 리더 연동 + DataTable</t>
         </is>
       </c>
       <c r="N30" s="2" t="n"/>
@@ -27433,31 +27209,18 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1) 룸명: 고유값, 2~20자
-2) 수용 인원: 1~100명
-3) 유형: PT룸/GX룸/다목적
-4) 예약 가능 시간: 요일별 개별 설정
-5) 미래 예약 존재 시 삭제 불가
-6) 삭제 시 관련 일정에서 룸 정보 자동 제거
-7) 비활성화: 신규 예약 차단 (기존 예약 유지)</t>
+          <t>1) 룸명 중복 불가
+2) 기존 예약 있으면 삭제 불가</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>룸명 중복: '이미 사용 중인 룸 이름입니다'
-수용 인원 범위 오류: '수용 인원은 1~100명으로 입력하세요'
-예약 있는 룸 삭제 시도: '미래 예약이 있어 삭제할 수 없습니다'
-저장 실패: '룸 정보 저장에 실패했습니다'</t>
+          <t>예약 존재 삭제: 에러 메시지</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET/POST/PATCH/DELETE /api/v1/rooms
-React Hook Form + Zod 룸 폼 검증
-요일별 시간 설정 UI (요일 체크박스 + 시간 범위)
-배치도 탭 – 드래그 배치 (react-dnd)
-삭제 확인 AlertDialog
-상태 토글 Switch 컴포넌트</t>
+          <t>Card + Modal CRUD</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
@@ -27568,31 +27331,18 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1) 역할 체계: 최고관리자/센터장/매니저/FC/스태프/조회전용
-2) 역할별 기본 권한 자동 배정
-3) 고용 유형: 정규직(월급)/계약직(월급+계약기간)/시간제(시급)
-4) 퇴사 처리 시 관리자 계정 자동 비활성화
-5) 담당 회원 재배정 알림 자동 발송
-6) 검색: 이름 부분일치, debounce 300ms
-7) 권한별 조회 범위 (FC: 본인 담당만)</t>
+          <t>1) branch_id 기준
+2) 센터장 이상만 접근</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 없음: '검색된 직원이 없습니다' Empty State
-권한 없음: 직원 등록/수정/삭제 버튼 비활성화
-퇴사 처리 확인: '퇴사 처리하면 계정이 비활성화됩니다. 진행하시겠습니까?'
-데이터 로드 실패: '직원 목록을 불러오지 못했습니다'</t>
+          <t>결과 없음: 빈 상태</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/staff
-DataTable (정렬, 필터, 다중선택)
-퇴사 처리 AlertDialog + useMutation
-useDebounce() (300ms) 검색
-역할별 색상 Badge
-근태/급여 탭 컴포넌트 분리</t>
+          <t>DataTable + React Query</t>
         </is>
       </c>
       <c r="N34" s="2" t="n"/>
@@ -27677,32 +27427,19 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1) 이메일 기반 관리자 계정 자동 생성 (등록 시)
-2) 역할 선택 시 기본 권한 자동 배정
-3) 연락처: 동일 지점 내 중복 불가
-4) 계약직: 계약 종료일 필수 입력
-5) 수정 시 변경 이력 자동 기록
-6) 프로필 사진: JPG/PNG, 5MB 이하
-7) 퇴사 후 데이터: 6개월 보관 후 삭제 or 영구 보관 (설정)</t>
+          <t>1) 역할별 기본 권한 자동 배정
+2) 관리자 계정 이메일 필수</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>이메일 중복: '이미 사용 중인 이메일입니다'
-연락처 중복: '이미 등록된 연락처입니다'
-계약 종료일 미입력 (계약직): '계약직은 계약 종료일이 필수입니다'
-저장 실패: '직원 정보 저장에 실패했습니다'
-취소 시: '변경사항이 있습니다. 나가시겠습니까?'</t>
+          <t>중복 이메일: 에러
+필수 미입력: 에러</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod (고용유형별 동적 스키마)
-useMutation – POST/PATCH /api/v1/staff
-이미지 업로드 – presigned URL
-역할 선택 시 권한 미리보기 표시
-4섹션 Accordion 폼 (인적사항/근무/급여/계정)
-useBlocker() – 미저장 이탈 방지</t>
+          <t>React Hook Form + 권한 미리보기</t>
         </is>
       </c>
       <c r="N35" s="2" t="n"/>
@@ -27819,32 +27556,18 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1) 실지급액 = 기본급 + 인센티브 + 수당 - 4대보험 - 소득세
-2) 인센티브: PT 건당 커미션 (예: 30%, 센터 설정)
-3) 급여 상태 흐름: 미정산 → 임시저장 → 확정대기 → 확정완료
-4) 확정완료 상태: 수정 불가 (최고관리자 해제 가능)
-5) 마감: 매월 25일 (센터 설정 가능)
-6) 이의제기: 직원 제출 → 관리자 재검토
-7) 권한: 센터장 이상만 전체 조회, FC는 본인만</t>
+          <t>1) 실지급액 = 기본급 + 인센티브 - 공제
+2) 지급 완료 시 수정 불가</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>확정완료 후 수정 시도: '확정된 급여는 수정할 수 없습니다 (관리자 해제 필요)'
-계산 오류: '급여 계산 중 오류가 발생했습니다'
-마감 후 수정: '마감 처리된 급여입니다'
-권한 없음: 타인 급여 조회 불가
-데이터 없음: '해당 월의 급여 데이터가 없습니다'</t>
+          <t>데이터 없음: 빈 상태</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/payroll
-월 선택 DatePicker (year/month)
-급여 계산 로직 (useMemo)
-상태 흐름 표시 – Step Indicator
-확정 처리 AlertDialog
-DataTable (97명, 가상화 – react-virtual)</t>
+          <t>DataTable + footer 합계</t>
         </is>
       </c>
       <c r="N37" s="2" t="n"/>
@@ -27924,30 +27647,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1) 명세서 조회 권한: 본인 or 센터장 이상
-2) 확정완료 후 자동 생성
-3) PDF 다운로드 지원
-4) 이메일 자동 발송 (설정 시)
-5) 이의제기 기능 제공
-6) 조회 이력 로깅</t>
+          <t>1) 본인 명세서만 조회 가능 (센터장 이상은 전체)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>본인 외 명세서 접근: '조회 권한이 없습니다'
-미확정 명세서: '아직 확정되지 않은 급여입니다'
-PDF 생성 실패: '명세서 PDF 생성에 실패했습니다'
-이메일 발송 실패: '이메일 발송에 실패했습니다. 직접 다운로드 해주세요'</t>
+          <t>명세서 없음: 안내</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/payroll/statement
-html2pdf.js – PDF 다운로드
-명세서 상세 모달 (Dialog)
-이의제기 Textarea 폼
-이메일 발송 – POST /api/v1/payroll/statement/send
-인쇄 – react-to-print</t>
+          <t>명세서 컴포넌트 + html2pdf</t>
         </is>
       </c>
       <c r="N38" s="2" t="n"/>
@@ -28059,33 +27769,20 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1) SMS: 최대 90자 (초과 시 LMS 자동 전환)
-2) LMS: 최대 2,000자
-3) 카카오 알림톡: 최대 1,000자
-4) 예약 발송: 최소 5분 후 ~ 최대 30일 후
-5) 발송 전 비용 사전 표시 (SMS 70원, LMS 30원, 카카오 8원)
-6) 치환 변수 지원: {이름}, {만료일}, {잔여일} 등
-7) 중복 발송 방지: 동일 수신자 + 동일 내용 5분 내 차단</t>
+          <t>1) SMS 90자, LMS 2000자 제한
+2) 발송 비용 사전 표시
+3) 예약 발송 지원</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>수신자 없음: '수신자를 선택해주세요'
-내용 없음: '메시지 내용을 입력해주세요'
-잔액 부족: '발송 잔액이 부족합니다. 충전 후 이용하세요'
-예약 시간 오류: '예약 시간은 5분 후부터 설정 가능합니다'
-발송 실패: '메시지 발송에 실패했습니다 (N건 실패)'</t>
+          <t>수신자 없음: 에러
+발송 실패: 실패 건 재발송</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form – 발송 폼
-useMutation – POST /api/v1/messages/send
-회원 선택 Combobox (다중선택, 검색)
-글자 수 카운터 + 자동 LMS 전환 표시
-치환 변수 삽입 버튼
-DateTimePicker – 예약 발송
-sonner 토스트 – 발송 결과</t>
+          <t>메시지 API + 변수 치환</t>
         </is>
       </c>
       <c r="N40" s="2" t="n"/>
@@ -28166,30 +27863,18 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1) 13종 트리거 정의 (만료 D-7/D-3/D-1/당일, 생일, 장기미출석 30일 등)
-2) 매일 오전 9시 스케줄러 실행
-3) 중복 방지: 동일 회원 + 동일 규칙 → 1일 1회만 발송
-4) 템플릿별 치환 변수 관리
-5) 채널별 개별 ON/OFF 설정 (SMS/카카오)
-6) 테스트 발송 기능 (본인 번호로)</t>
+          <t>1) 매일 오전 9시 자동 실행
+2) 중복 발송 방지 (동일 회원 동일 규칙 1회/일)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>템플릿 내 잘못된 변수: '유효하지 않은 치환 변수입니다: {변수명}'
-발송 채널 미선택: '최소 1개의 발송 채널을 선택하세요'
-테스트 발송 실패: '테스트 발송에 실패했습니다'
-저장 실패: '알림 설정 저장에 실패했습니다'</t>
+          <t>템플릿 미입력: 에러</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Toggle Switch 컴포넌트 (13종 ON/OFF)
-템플릿 편집 모달 (Textarea + 변수 삽입)
-useMutation – PATCH /api/v1/auto-alarms
-미리보기 렌더링 (치환 변수 치환 표시)
-테스트 발송 버튼 + 로딩 상태
-TanStack Query – GET /api/v1/auto-alarms</t>
+          <t>규칙 엔진 + 스케줄러</t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
@@ -28302,33 +27987,19 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1) 쿠폰 유형: 정률(%)/정액(원)/무료 이용권
-2) 유효기간: 특정 기간 or 발급일+N일
-3) 사용 한도: 전체 N회 or 회원당 1회
-4) 최소 주문 금액 설정 가능
-5) 만료 쿠폰 자동 비활성화 (매일 자정)
-6) 발급 건수 1개 이상인 쿠폰 삭제 불가
-7) 쿠폰 코드: 8자리 영숫자 자동 생성</t>
+          <t>1) 만료 쿠폰 자동 비활성화
+2) 사용 한도 도달 시 자동 마감</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>발급 건수 있는 쿠폰 삭제: '발급된 쿠폰이 있어 삭제할 수 없습니다'
-중복 쿠폰명: '이미 사용 중인 쿠폰 이름입니다'
-할인율 범위 오류: '할인율은 1~100% 범위로 입력하세요'
-최소 금액 이하 사용 시도: '최소 주문 금액(N원) 이상에서 사용 가능합니다'
-만료 쿠폰 사용: '만료된 쿠폰입니다'
-한도 초과: '쿠폰 사용 한도를 초과했습니다'</t>
+          <t>만료 쿠폰 사용: 에러
+한도 초과: 에러</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>React Hook Form + Zod (유형별 동적 폼)
-useMutation – POST/PATCH/DELETE /api/v1/coupons
-쿠폰 코드 자동 생성 버튼 (nanoid)
-발급 모달 – 대상 회원 다중선택
-DataTable – 쿠폰 목록/발급 이력
-만료일 자동 계산 (발급일+N일)</t>
+          <t>CRUD + DataTable</t>
         </is>
       </c>
       <c r="N43" s="2" t="n"/>
@@ -28409,32 +28080,19 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1) 기본 적립률: 결제금액의 N% (센터 설정)
-2) 유효기간: N개월 기본 12개월
-3) 최소 사용: 1,000원 이상
-4) 최대 사용: 결제금액의 50% (센터 설정)
-5) 현금 전환 불가
-6) 만료 마일리지 자동 소멸 (매일 자정)
-7) 수동 처리: 적립/차감 사유 필수 입력</t>
+          <t>1) 잔액 부족 시 차감 불가
+2) 결제 시 자동 적립률 설정 가능</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>잔액 부족: '사용 가능한 마일리지가 부족합니다 (잔액: N원)'
-최소 사용 미달: '마일리지는 최소 1,000원 이상 사용 가능합니다'
-최대 사용 초과: '결제금액의 50%까지만 마일리지 사용 가능합니다'
-만료 마일리지: '만료된 마일리지는 사용할 수 없습니다'
-수동 처리 사유 미입력: '사유를 입력해주세요'</t>
+          <t>잔액 부족: 에러
+음수 입력: 에러</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/mileage
-수동 처리 모달 (React Hook Form)
-적립/차감 이력 DataTable
-정책 설정 폼 – useMutation PATCH /api/v1/mileage/policy
-만료 예정 마일리지 경고 표시
-Intl.NumberFormat – 마일리지 금액 포맷</t>
+          <t>모달 + DataTable</t>
         </is>
       </c>
       <c r="N44" s="2" t="n"/>
@@ -28546,34 +28204,20 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1) 계약 5단계: 회원선택 → 상품선택 → 기간/금액설정 → 결제 → 전자서명
-2) 할인 최대 50%, 할인 사유 필수 입력
-3) 할인 유형: 재등록/신규/이벤트/관리자 재량
-4) 계약 완료 시 이용권 자동 생성
-5) 매출 자동 등록
-6) 마일리지 자동 적립 (설정 시)
-7) 환영 메시지 자동 발송 (설정 시)
-8) 계약서 PDF 자동 생성 및 저장</t>
+          <t>1) 계약 시작일 기준 이용권 자동 생성
+2) 할인 최대 50%
+3) 결제 완료 시 매출 자동 등록</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>회원 미선택: '회원을 먼저 선택해주세요'
-상품 미선택: '상품을 1개 이상 선택해주세요'
-할인 50% 초과: '할인율은 최대 50%까지 가능합니다'
-할인 사유 미입력: '할인 사유를 입력해주세요'
-서명 미완료: '전자서명을 완료해주세요'
-결제 실패: '결제 처리에 실패했습니다'</t>
+          <t>결제 실패: 계약 보류
+이전 단계 미완료: 다음 진행 불가</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5단계 Stepper 컴포넌트
-useMutation – POST /api/v1/contracts
-회원 검색 Combobox
-서명 패드 – react-signature-canvas
-계약서 PDF – html2pdf.js
-Zustand contractStore (5단계 상태 유지)</t>
+          <t>Stepper + React Hook Form + 결제 API</t>
         </is>
       </c>
       <c r="N46" s="2" t="n"/>
@@ -28659,30 +28303,19 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1) 플랜: Starter(회원 200명, 지점 1개)/Pro(1,000명, 3개)/Enterprise(무제한)
-2) 연간 결제 시 20% 할인
-3) 다운그레이드: 현재 사용량이 하위 플랜 제한 이하일 때만 가능
-4) 구독 취소: 현재 기간 만료까지 사용 가능
-5) 사용량 초과 시 업그레이드 안내
-6) 결제 수단 등록 필수 (카드)</t>
+          <t>1) 자동 결제 실패 시 3일 내 재시도
+2) 3회 실패 시 구독 일시정지</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>다운그레이드 불가: '현재 회원 수(N명)가 하위 플랜 제한을 초과합니다'
-결제 실패: '결제 처리에 실패했습니다. 카드 정보를 확인하세요'
-구독 취소 확인: '취소 시 현재 기간(~날짜) 만료 후 서비스가 종료됩니다'
-사용량 초과: '현재 플랜의 회원 수 한도에 도달했습니다. 업그레이드가 필요합니다'</t>
+          <t>결제 실패: 회원 알림
+해지: 잔여 기간 환불 계산</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>플랜 비교 카드 UI (Starter/Pro/Enterprise)
-사용량 Progress Bar (회원수, 지점수)
-결제 수단 관리 – Stripe 또는 토스페이먼츠
-플랜 변경 AlertDialog
-인보이스 목록 DataTable
-인보이스 PDF 다운로드</t>
+          <t>DataTable + Modal + 결제 스케줄러</t>
         </is>
       </c>
       <c r="N47" s="2" t="n"/>
@@ -28793,33 +28426,18 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1) 설정 변경 시 즉시 반영 (페이지 새로고침 불필요)
-2) 이미지 업로드: JPG/PNG, 2MB 이하
-3) 주소: Kakao 주소 API 연동
-4) 카드 단말기 연결 테스트 기능
-5) 출입문 목록 관리 (IoT 연동)
-6) 설정 변경 이력 로깅
-7) 7개 탭: 기본/출입문/키오스크/앱/알림/권한/기타</t>
+          <t>1) 설정 변경 즉시 반영
+2) 변경 이력 기록</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>이미지 크기 초과: '이미지는 2MB 이하만 업로드 가능합니다'
-필수 항목 미입력: '센터명은 필수 입력 항목입니다'
-저장 실패: '설정 저장에 실패했습니다'
-카드 단말기 연결 실패: '단말기 연결을 확인하세요'
-권한 없음: 설정 메뉴 접근 불가 (매니저 이하)</t>
+          <t>저장 실패: 재시도</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET /api/v1/settings
-useMutation – PATCH /api/v1/settings
-Tabs 컴포넌트 (7탭, URL 동기화)
-이미지 업로드 + 미리보기
-Kakao 주소 API
-React Hook Form (탭별 폼 분리)
-저장 성공 sonner 토스트</t>
+          <t>Tab + Form</t>
         </is>
       </c>
       <c r="N49" s="2" t="n"/>
@@ -28900,30 +28518,19 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1) 권한 매트릭스: 6역할 × 10메뉴 × CRUD 조합
-2) 최고관리자 권한 수정 불가
-3) 커스텀 역할 생성 가능
-4) 변경 감지 후 저장 버튼 활성화
-5) 변경 이력 로깅
-6) 역할 복사 기능</t>
+          <t>1) 최고관리자 권한 변경 불가
+2) 하위 역할에 상위 권한 부여 불가</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>최고관리자 권한 수정 시도: '최고관리자 권한은 수정할 수 없습니다'
-권한 충돌: '하위 역할에 상위 역할보다 높은 권한을 부여할 수 없습니다'
-저장 실패: '권한 설정 저장에 실패했습니다'
-역할 삭제 시 소속 직원 있음: '소속 직원이 있어 역할을 삭제할 수 없습니다'</t>
+          <t>권한 충돌: 경고
+자기 자신 권한 축소: 확인 모달</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>권한 매트릭스 테이블 (Checkbox 그리드)
-useMutation – PATCH /api/v1/permissions
-변경 감지 (dirtyFields)
-전체 허용/차단 토글 버튼
-커스텀 역할 추가 모달
-역할 복사 기능</t>
+          <t>체크박스 매트릭스 + API</t>
         </is>
       </c>
       <c r="N50" s="2" t="n"/>
@@ -29003,31 +28610,19 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1) 체크인 방식: QR코드/RFID/바코드/전화번호
-2) 대기 화면: 로고+공지사항+광고 배너 슬라이드
-3) 체크인 성공: TTS 음성 + 환영 메시지
-4) 체크인 실패: TTS 음성 + 거부 사유 표시
-5) 자동 로그아웃: 10초 (설정 가능)
-6) 테마/폰트 크기 설정 가능
-7) 기기별 설정 독립 관리</t>
+          <t>1) 이미지 5MB 이하
+2) JPG/PNG만 허용</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>TTS 지원 불가 브라우저: TTS 없이 텍스트만 표시
-이미지 업로드 실패: '이미지 업로드에 실패했습니다'
-키오스크 연결 실패: '키오스크 기기와 연결할 수 없습니다'
-저장 실패: '키오스크 설정 저장에 실패했습니다'</t>
+          <t>용량 초과: 에러
+형식 오류: 에러</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Web Speech API (TTS – speechSynthesis)
-useMutation – PATCH /api/v1/kiosk/settings
-이미지 업로드 + 미리보기 (배너/로고)
-키오스크 미리보기 모달
-4탭 (기본/화면/TTS/출입규칙)
-자동 로그아웃 타이머 설정 Slider</t>
+          <t>FileUpload + Preview</t>
         </is>
       </c>
       <c r="N51" s="2" t="n"/>
@@ -29107,31 +28702,18 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1) IoT 출입문 연결 상태: 5분 주기 갱신
-2) 오프라인 30분 이상 → 관리자 알림
-3) 원격 개방: 관리자 권한만 가능
-4) 비상 해제: 화재/정전 시 전체 개방
-5) 출입 로그: 실시간 기록
-6) 기기 유형: 게이트/카메라/체성분계/기타</t>
+          <t>1) 기기 IP/포트 유효성 검증
+2) 연결 상태 5분 주기 갱신</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>IoT 기기 오프라인: '기기가 오프라인 상태입니다 (30분 이상)'
-원격 개방 권한 없음: '원격 개방은 관리자 권한이 필요합니다'
-원격 개방 확인: '출입문을 원격으로 개방하시겠습니까?'
-기기 연결 실패: '기기 연결에 실패했습니다'
-설정 저장 실패: 'IoT 설정 저장에 실패했습니다'</t>
+          <t>연결 실패: 재시도 안내</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>WebSocket – 실시간 기기 상태 모니터링
-TanStack Query (5분 refetchInterval) – 기기 상태
-원격 개방 AlertDialog + useMutation
-출입 로그 DataTable (실시간 갱신)
-기기 상태 색상 표시 (온라인/오프라인/경고)
-4탭 (게이트/기기/로그/규칙)</t>
+          <t>DataTable + 상태 아이콘 + ping API</t>
         </is>
       </c>
       <c r="N52" s="2" t="n"/>
@@ -29212,33 +28794,20 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1) 지점 코드: 영문 2~5자 고유값
-2) 지점별 데이터 완전 격리 (멀티테넌트 – branch_id)
-3) 지점 비활성화: 소속 데이터 유지, 로그인 차단
-4) 데이터 초기화: 최고관리자 + 비밀번호 확인 + 2중 확인 필수
-5) 회원 지점 이동: 이용권 유지 or 신규 발급 선택
-6) 지점 통합 현황 통계 (전체 지점 합산)
-7) 최고관리자만 지점 생성/삭제 가능</t>
+          <t>1) 지점 코드 고유
+2) 지점별 데이터 완전 격리
+3) 데이터 초기화 시 2중 확인</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>지점 코드 중복: '이미 사용 중인 지점 코드입니다'
-지점 코드 형식 오류: '지점 코드는 영문 2~5자로 입력하세요'
-비활성 지점 로그인: '비활성화된 지점입니다. 관리자에게 문의하세요'
-데이터 초기화 확인: '지점명을 입력하여 초기화를 확인하세요'
-지점 삭제 (회원 있음): '소속 회원이 있어 삭제할 수 없습니다'
-권한 없음: '지점 관리는 최고관리자만 가능합니다'</t>
+          <t>중복 코드: 에러
+데이터 존재 삭제: 비활성화만 가능</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>TanStack Query – GET/POST/PATCH/DELETE /api/v1/branches
-지점 등록 모달 (React Hook Form + Zod)
-지점 이동 신청 모달 (이용권 처리 선택)
-데이터 초기화 – 텍스트 확인 입력 + 2중 AlertDialog
-통합 통계 카드 (전체 지점 합산)
-3탭 (목록/통합/이동) + 매출 비교 차트</t>
+          <t>Card/Table + Modal CRUD</t>
         </is>
       </c>
       <c r="N53" s="2" t="n"/>
@@ -30831,25 +30400,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-    </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -30861,21 +30412,6 @@
           <t>키오스크 입장 (1개 기능)</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -30950,34 +30486,13 @@
           <t>얼굴인식 SDK + NFC Reader</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -30989,21 +30504,6 @@
           <t>키오스크 퇴장 (1개 기능)</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -31064,36 +30564,13 @@
           <t>퇴장 미처리 시 마감 일괄 퇴장 처리</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
@@ -31105,21 +30582,6 @@
           <t>키오스크 골프 타석 예약 (1개 기능)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -31193,34 +30655,13 @@
           <t>실시간 WebSocket + 타석 배치도 UI</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -31232,21 +30673,6 @@
           <t>키오스크 사물함 확인 (1개 기능)</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -31312,35 +30738,13 @@
           <t>미배정 시: 자동 배정 후 표시</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
@@ -31352,21 +30756,6 @@
           <t>키오스크 1일권 결제 (1개 기능)</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -31441,34 +30830,13 @@
           <t>PG SDK + 간편결제 모듈</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
@@ -31480,21 +30848,6 @@
           <t>키오스크 GX 예약 (1개 기능)</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -31563,35 +30916,13 @@
           <t>잔여 횟수 0: '이용권을 구매해주세요' 안내</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -31603,21 +30934,6 @@
           <t>키오스크 골프 타석 입장 (1개 기능)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -31686,35 +31002,13 @@
           <t>예약 없음: '예약 후 이용해주세요' 안내</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -31726,21 +31020,6 @@
           <t>앱 홈 (1개 기능)</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -31812,34 +31091,13 @@
           <t>React Native</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="118"/>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
@@ -31851,21 +31109,6 @@
           <t>앱 QR 입장 (1개 기능)</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -31936,34 +31179,13 @@
           <t>QR 생성 라이브러리</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -31975,21 +31197,6 @@
           <t>앱 GX 예약 (1개 기능)</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -32064,34 +31271,13 @@
           <t>React Native + 좌석 배치 SVG</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
@@ -32103,21 +31289,6 @@
           <t>앱 골프 예약 (1개 기능)</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -32184,35 +31355,13 @@
           <t>입장 시한 초과: 자동 취소 + 다음 대기자</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
@@ -32224,21 +31373,6 @@
           <t>앱 레슨 예약/서명 (1개 기능)</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -32311,34 +31445,13 @@
           <t>Canvas 서명 + FCM Push</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -32350,21 +31463,6 @@
           <t>트레이너 앱 홈 (1개 기능)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -32425,40 +31523,18 @@
           <t>수업 10분 전 알림 자동 발송</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>React Native</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="133"/>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
@@ -32470,21 +31546,6 @@
           <t>트레이너 레슨 기록 (1개 기능)</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -32558,34 +31619,13 @@
           <t>Canvas 서명 + FCM + 카메라</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -32597,21 +31637,6 @@
           <t>트레이너 스케줄 (1개 기능)</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -32678,35 +31703,13 @@
           <t>예약 거절 시 회원에게 자동 알림</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="139"/>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
@@ -32718,21 +31721,6 @@
           <t>FC 앱 홈 (1개 기능)</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -32805,34 +31793,13 @@
           <t>FCM Push + WebSocket</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="142"/>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
@@ -32844,21 +31811,6 @@
           <t>FC 즐겨찾기 알림 (1개 기능)</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -32927,35 +31879,13 @@
           <t>해당 회원 없음: 검색 결과 없음 안내</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -32967,21 +31897,6 @@
           <t>FC 상담 기록 (1개 기능)</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -33044,16 +31959,11 @@
 2) 상담 기록 수정: 24시간 이내만 가능</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
